--- a/DATA/analysis/page7小结/page7_分组汇总_2026-08-14_最终.xlsx
+++ b/DATA/analysis/page7小结/page7_分组汇总_2026-08-14_最终.xlsx
@@ -2,30 +2,57 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="2610" yWindow="3135" windowWidth="28740" windowHeight="16590" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1原表" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2分类表" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3体检诉求对比表" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3体检诉求对比" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="8">
+  <fonts count="9">
     <font>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <i val="1"/>
+      <color rgb="FF808080"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <family val="3"/>
+      <sz val="9"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+      <family val="2"/>
+      <b val="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+      <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
     </font>
     <font>
       <b val="1"/>
@@ -43,20 +70,8 @@
       <b val="1"/>
       <color rgb="00C55A11"/>
     </font>
-    <font>
-      <name val="Consolas"/>
-      <color rgb="001F4E79"/>
-    </font>
-    <font>
-      <name val="Consolas"/>
-      <color rgb="00C55A11"/>
-    </font>
-    <font>
-      <color rgb="00666666"/>
-      <sz val="9"/>
-    </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill/>
     </fill>
@@ -65,7 +80,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFEDEDED"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00404040"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C00000"/>
       </patternFill>
     </fill>
     <fill>
@@ -75,7 +100,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="001F4E79"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00E3EDF7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C55A11"/>
       </patternFill>
     </fill>
     <fill>
@@ -83,28 +118,94 @@
         <fgColor rgb="00FDEBD9"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00C00000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="001F4E79"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00C55A11"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="2">
+  <borders count="9">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFD9D9D9"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFD9D9D9"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFD9D9D9"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFD9D9D9"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFD9D9D9"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFD9D9D9"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFD9D9D9"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFD9D9D9"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFD9D9D9"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFD9D9D9"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FFD9D9D9"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFD9D9D9"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFD9D9D9"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFD9D9D9"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFD9D9D9"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFD9D9D9"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -125,83 +226,65 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -564,825 +647,900 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J22"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:K25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="13.5"/>
   <cols>
-    <col width="5" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
     <col width="7" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="9" customWidth="1" min="8" max="8"/>
-    <col width="9" customWidth="1" min="9" max="9"/>
-    <col width="18" customWidth="1" min="10" max="10"/>
+    <col width="12.625" customWidth="1" min="4" max="7"/>
+    <col width="10" customWidth="1" min="8" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
+    <col width="9" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="39" customHeight="1">
+      <c r="A1" s="3" t="inlineStr">
         <is>
           <t>序号</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="3" t="inlineStr">
         <is>
           <t>名称</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="3" t="inlineStr">
         <is>
           <t>楼栋</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="3" t="inlineStr">
         <is>
           <t>安全韧性问题
-（每百栋）</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="n"/>
-      <c r="F1" s="1" t="inlineStr">
+（每百栋问题数）</t>
+        </is>
+      </c>
+      <c r="E1" s="5" t="n"/>
+      <c r="F1" s="3" t="inlineStr">
         <is>
           <t>民生基础需求
-（每百栋）</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="n"/>
-      <c r="H1" s="1" t="inlineStr">
+（每百栋需求数）</t>
+        </is>
+      </c>
+      <c r="G1" s="5" t="n"/>
+      <c r="H1" s="3" t="inlineStr">
         <is>
           <t>问题指标</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" s="3" t="inlineStr">
         <is>
           <t>群众诉求</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" s="3" t="inlineStr">
         <is>
           <t>评估</t>
         </is>
       </c>
-    </row>
-    <row r="2">
-      <c r="D2" s="1" t="inlineStr">
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>备注</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="18" customHeight="1">
+      <c r="A2" s="6" t="n"/>
+      <c r="B2" s="6" t="n"/>
+      <c r="C2" s="6" t="n"/>
+      <c r="D2" s="3" t="inlineStr">
         <is>
           <t>体检</t>
         </is>
       </c>
-      <c r="E2" s="1" t="inlineStr">
+      <c r="E2" s="3" t="inlineStr">
         <is>
           <t>诉求</t>
         </is>
       </c>
-      <c r="F2" s="1" t="inlineStr">
+      <c r="F2" s="3" t="inlineStr">
         <is>
           <t>体检</t>
         </is>
       </c>
-      <c r="G2" s="1" t="inlineStr">
+      <c r="G2" s="3" t="inlineStr">
         <is>
           <t>诉求</t>
         </is>
       </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="n">
+      <c r="H2" s="6" t="n"/>
+      <c r="I2" s="6" t="n"/>
+      <c r="J2" s="6" t="n"/>
+      <c r="K2" s="6" t="n"/>
+    </row>
+    <row r="3" ht="30" customHeight="1">
+      <c r="A3" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" s="4" t="inlineStr">
         <is>
           <t>营盘路社区</t>
         </is>
       </c>
-      <c r="C3" s="2" t="n">
+      <c r="C3" s="4" t="n">
         <v>66</v>
       </c>
-      <c r="D3" s="2" t="n">
+      <c r="D3" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="E3" s="2" t="n">
+      <c r="E3" s="4" t="n">
         <v>15.2</v>
       </c>
-      <c r="F3" s="2" t="n">
+      <c r="F3" s="4" t="n">
         <v>56.1</v>
       </c>
-      <c r="G3" s="2" t="n">
+      <c r="G3" s="4" t="n">
         <v>162.1</v>
       </c>
-      <c r="H3" s="2" t="n">
+      <c r="H3" s="4" t="n">
         <v>37</v>
       </c>
-      <c r="I3" s="2" t="n">
+      <c r="I3" s="4" t="n">
         <v>117</v>
       </c>
       <c r="J3" s="4" t="inlineStr">
         <is>
-          <t>双高 ★</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="n">
+          <t>双高</t>
+        </is>
+      </c>
+      <c r="K3" s="4" t="n"/>
+    </row>
+    <row r="4" ht="30" customHeight="1">
+      <c r="A4" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" s="4" t="inlineStr">
         <is>
           <t>宝联社区</t>
         </is>
       </c>
-      <c r="C4" s="2" t="n">
+      <c r="C4" s="4" t="n">
         <v>94</v>
       </c>
-      <c r="D4" s="2" t="n">
+      <c r="D4" s="4" t="n">
         <v>3.2</v>
       </c>
-      <c r="E4" s="2" t="n">
+      <c r="E4" s="4" t="n">
         <v>30.9</v>
       </c>
-      <c r="F4" s="2" t="n">
+      <c r="F4" s="4" t="n">
         <v>27.7</v>
       </c>
-      <c r="G4" s="2" t="n">
+      <c r="G4" s="4" t="n">
         <v>135.1</v>
       </c>
-      <c r="H4" s="2" t="n">
+      <c r="H4" s="4" t="n">
         <v>29</v>
       </c>
-      <c r="I4" s="2" t="n">
+      <c r="I4" s="4" t="n">
         <v>156</v>
       </c>
       <c r="J4" s="4" t="inlineStr">
         <is>
-          <t>双高 ★</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="n">
+          <t>双高</t>
+        </is>
+      </c>
+      <c r="K4" s="4" t="n"/>
+    </row>
+    <row r="5" ht="30" customHeight="1">
+      <c r="A5" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B5" s="4" t="inlineStr">
         <is>
           <t>汕头路社区</t>
         </is>
       </c>
-      <c r="C5" s="2" t="n">
+      <c r="C5" s="4" t="n">
         <v>39</v>
       </c>
-      <c r="D5" s="2" t="n">
+      <c r="D5" s="4" t="n">
         <v>35.9</v>
       </c>
-      <c r="E5" s="2" t="n">
+      <c r="E5" s="4" t="n">
         <v>25.6</v>
       </c>
-      <c r="F5" s="2" t="n">
+      <c r="F5" s="4" t="n">
         <v>7.7</v>
       </c>
-      <c r="G5" s="2" t="n">
+      <c r="G5" s="4" t="n">
         <v>248.7</v>
       </c>
-      <c r="H5" s="2" t="n">
+      <c r="H5" s="4" t="n">
         <v>17</v>
       </c>
-      <c r="I5" s="2" t="n">
+      <c r="I5" s="4" t="n">
         <v>107</v>
       </c>
       <c r="J5" s="4" t="inlineStr">
         <is>
-          <t>双高 ★</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="n">
+          <t>双高</t>
+        </is>
+      </c>
+      <c r="K5" s="4" t="n"/>
+    </row>
+    <row r="6" ht="30" customHeight="1">
+      <c r="A6" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B6" s="4" t="inlineStr">
         <is>
           <t>胜利四路社区</t>
         </is>
       </c>
-      <c r="C6" s="2" t="n">
+      <c r="C6" s="4" t="n">
         <v>44</v>
       </c>
-      <c r="D6" s="2" t="n">
+      <c r="D6" s="4" t="n">
         <v>13.6</v>
       </c>
-      <c r="E6" s="2" t="n">
+      <c r="E6" s="4" t="n">
         <v>45.5</v>
       </c>
-      <c r="F6" s="2" t="n">
+      <c r="F6" s="4" t="n">
         <v>22.7</v>
       </c>
-      <c r="G6" s="2" t="n">
+      <c r="G6" s="4" t="n">
         <v>215.9</v>
       </c>
-      <c r="H6" s="2" t="n">
+      <c r="H6" s="4" t="n">
         <v>16</v>
       </c>
-      <c r="I6" s="2" t="n">
+      <c r="I6" s="4" t="n">
         <v>115</v>
       </c>
       <c r="J6" s="4" t="inlineStr">
         <is>
-          <t>双高 ★</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="n">
+          <t>双高</t>
+        </is>
+      </c>
+      <c r="K6" s="4" t="n"/>
+    </row>
+    <row r="7" ht="30" customHeight="1">
+      <c r="A7" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B7" s="4" t="inlineStr">
         <is>
           <t>胜利二路社区</t>
         </is>
       </c>
-      <c r="C7" s="2" t="n">
+      <c r="C7" s="4" t="n">
         <v>30</v>
       </c>
-      <c r="D7" s="2" t="n">
+      <c r="D7" s="4" t="n">
         <v>20</v>
       </c>
-      <c r="E7" s="2" t="n">
+      <c r="E7" s="4" t="n">
         <v>30</v>
       </c>
-      <c r="F7" s="2" t="n">
+      <c r="F7" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="G7" s="2" t="n">
+      <c r="G7" s="4" t="n">
         <v>340</v>
       </c>
-      <c r="H7" s="2" t="n">
+      <c r="H7" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="I7" s="2" t="n">
+      <c r="I7" s="4" t="n">
         <v>111</v>
       </c>
       <c r="J7" s="4" t="inlineStr">
         <is>
-          <t>双高 ★</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="5" t="n">
+          <t>双高</t>
+        </is>
+      </c>
+      <c r="K7" s="4" t="n"/>
+    </row>
+    <row r="8" ht="30" customHeight="1">
+      <c r="A8" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="B8" s="6" t="inlineStr">
+      <c r="B8" s="4" t="inlineStr">
         <is>
           <t>深圳路社区</t>
         </is>
       </c>
-      <c r="C8" s="5" t="n">
+      <c r="C8" s="4" t="n">
         <v>127</v>
       </c>
-      <c r="D8" s="5" t="n">
+      <c r="D8" s="4" t="n">
         <v>61.4</v>
       </c>
-      <c r="E8" s="5" t="n">
+      <c r="E8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" s="4" t="n">
+        <v>22.8</v>
+      </c>
+      <c r="G8" s="4" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="H8" s="4" t="n">
+        <v>107</v>
+      </c>
+      <c r="I8" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="J8" s="4" t="inlineStr">
+        <is>
+          <t>客观隐患高·诉求未暴露</t>
+        </is>
+      </c>
+      <c r="K8" s="4" t="n"/>
+    </row>
+    <row r="9" ht="30" customHeight="1">
+      <c r="A9" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>西峡社区</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="n">
+        <v>78</v>
+      </c>
+      <c r="D9" s="4" t="n">
+        <v>105.1</v>
+      </c>
+      <c r="E9" s="4" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="F9" s="4" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="G9" s="4" t="n">
+        <v>39.7</v>
+      </c>
+      <c r="H9" s="4" t="n">
+        <v>91</v>
+      </c>
+      <c r="I9" s="4" t="n">
+        <v>35</v>
+      </c>
+      <c r="J9" s="4" t="inlineStr">
+        <is>
+          <t>客观隐患高·诉求未暴露</t>
+        </is>
+      </c>
+      <c r="K9" s="4" t="n"/>
+    </row>
+    <row r="10" ht="30" customHeight="1">
+      <c r="A10" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>金安岭社区</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="n">
+        <v>56</v>
+      </c>
+      <c r="D10" s="4" t="n">
+        <v>130.4</v>
+      </c>
+      <c r="E10" s="4" t="n">
+        <v>16.1</v>
+      </c>
+      <c r="F10" s="4" t="n">
+        <v>19.6</v>
+      </c>
+      <c r="G10" s="4" t="n">
+        <v>19.6</v>
+      </c>
+      <c r="H10" s="4" t="n">
+        <v>84</v>
+      </c>
+      <c r="I10" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="J10" s="4" t="inlineStr">
+        <is>
+          <t>客观隐患高·诉求未暴露</t>
+        </is>
+      </c>
+      <c r="K10" s="4" t="n"/>
+    </row>
+    <row r="11" ht="30" customHeight="1">
+      <c r="A11" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>镇境山社区</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="n">
+        <v>78</v>
+      </c>
+      <c r="D11" s="4" t="n">
+        <v>85.90000000000001</v>
+      </c>
+      <c r="E11" s="4" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="F11" s="4" t="n">
+        <v>19.2</v>
+      </c>
+      <c r="G11" s="4" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="H11" s="4" t="n">
+        <v>82</v>
+      </c>
+      <c r="I11" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="J11" s="4" t="inlineStr">
+        <is>
+          <t>客观隐患高·诉求未暴露</t>
+        </is>
+      </c>
+      <c r="K11" s="4" t="n"/>
+    </row>
+    <row r="12" ht="30" customHeight="1">
+      <c r="A12" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>幸福路社区</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="n">
+        <v>58</v>
+      </c>
+      <c r="D12" s="4" t="n">
+        <v>82.8</v>
+      </c>
+      <c r="E12" s="4" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="F12" s="4" t="n">
+        <v>29.3</v>
+      </c>
+      <c r="G12" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" s="4" t="n">
+        <v>65</v>
+      </c>
+      <c r="I12" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J12" s="4" t="inlineStr">
+        <is>
+          <t>客观隐患高·诉求未暴露</t>
+        </is>
+      </c>
+      <c r="K12" s="4" t="n"/>
+    </row>
+    <row r="13" ht="30" customHeight="1">
+      <c r="A13" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>新隆康路社区</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="n">
+        <v>130</v>
+      </c>
+      <c r="D13" s="4" t="n">
+        <v>36.2</v>
+      </c>
+      <c r="E13" s="4" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="F13" s="4" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="G13" s="4" t="n">
+        <v>42.3</v>
+      </c>
+      <c r="H13" s="4" t="n">
+        <v>62</v>
+      </c>
+      <c r="I13" s="4" t="n">
+        <v>64</v>
+      </c>
+      <c r="J13" s="4" t="inlineStr">
+        <is>
+          <t>客观隐患高·诉求未暴露</t>
+        </is>
+      </c>
+      <c r="K13" s="4" t="n"/>
+    </row>
+    <row r="14" ht="30" customHeight="1">
+      <c r="A14" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>果园路社区</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="n">
+        <v>93</v>
+      </c>
+      <c r="D14" s="4" t="n">
+        <v>26.9</v>
+      </c>
+      <c r="E14" s="4" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="F14" s="4" t="n">
+        <v>28</v>
+      </c>
+      <c r="G14" s="4" t="n">
+        <v>66.7</v>
+      </c>
+      <c r="H14" s="4" t="n">
+        <v>51</v>
+      </c>
+      <c r="I14" s="4" t="n">
+        <v>73</v>
+      </c>
+      <c r="J14" s="4" t="inlineStr">
+        <is>
+          <t>客观隐患高·诉求未暴露</t>
+        </is>
+      </c>
+      <c r="K14" s="4" t="n"/>
+    </row>
+    <row r="15" ht="30" customHeight="1">
+      <c r="A15" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>桥北社区</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="n">
+        <v>48</v>
+      </c>
+      <c r="D15" s="4" t="n">
+        <v>35.4</v>
+      </c>
+      <c r="E15" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" s="4" t="n">
+        <v>41.7</v>
+      </c>
+      <c r="G15" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" s="4" t="n">
+        <v>37</v>
+      </c>
+      <c r="I15" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" s="4" t="inlineStr">
+        <is>
+          <t>客观隐患高·诉求未暴露</t>
+        </is>
+      </c>
+      <c r="K15" s="4" t="n"/>
+    </row>
+    <row r="16" ht="30" customHeight="1">
+      <c r="A16" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>朝阳路社区</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="n">
+        <v>84</v>
+      </c>
+      <c r="D16" s="4" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="E16" s="4" t="n">
+        <v>69</v>
+      </c>
+      <c r="F16" s="4" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="G16" s="4" t="n">
+        <v>638.1</v>
+      </c>
+      <c r="H16" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="I16" s="4" t="n">
+        <v>594</v>
+      </c>
+      <c r="J16" s="4" t="inlineStr">
+        <is>
+          <t>主观诉求高·体检未印证</t>
+        </is>
+      </c>
+      <c r="K16" s="4" t="n"/>
+    </row>
+    <row r="17" ht="30" customHeight="1">
+      <c r="A17" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>万达社区</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="n">
+        <v>69</v>
+      </c>
+      <c r="D17" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" s="4" t="n">
+        <v>72.5</v>
+      </c>
+      <c r="F17" s="4" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="G17" s="4" t="n">
+        <v>653.6</v>
+      </c>
+      <c r="H17" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="I17" s="4" t="n">
+        <v>501</v>
+      </c>
+      <c r="J17" s="4" t="inlineStr">
+        <is>
+          <t>主观诉求高·体检未印证</t>
+        </is>
+      </c>
+      <c r="K17" s="4" t="n"/>
+    </row>
+    <row r="18" ht="30" customHeight="1">
+      <c r="A18" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>港务社区</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="n">
+        <v>106</v>
+      </c>
+      <c r="D18" s="4" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="E18" s="4" t="n">
+        <v>78.3</v>
+      </c>
+      <c r="F18" s="4" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="G18" s="4" t="n">
+        <v>315.1</v>
+      </c>
+      <c r="H18" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="I18" s="4" t="n">
+        <v>417</v>
+      </c>
+      <c r="J18" s="4" t="inlineStr">
+        <is>
+          <t>主观诉求高·体检未印证</t>
+        </is>
+      </c>
+      <c r="K18" s="4" t="n"/>
+    </row>
+    <row r="19" ht="30" customHeight="1">
+      <c r="A19" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>建设社区</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="n">
+        <v>66</v>
+      </c>
+      <c r="D19" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" s="4" t="n">
+        <v>78.8</v>
+      </c>
+      <c r="F19" s="4" t="n">
+        <v>13.6</v>
+      </c>
+      <c r="G19" s="4" t="n">
+        <v>484.8</v>
+      </c>
+      <c r="H19" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="I19" s="4" t="n">
+        <v>372</v>
+      </c>
+      <c r="J19" s="4" t="inlineStr">
+        <is>
+          <t>主观诉求高·体检未印证</t>
+        </is>
+      </c>
+      <c r="K19" s="4" t="n"/>
+    </row>
+    <row r="20" ht="30" customHeight="1">
+      <c r="A20" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>岳湾路社区</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="n">
+        <v>83</v>
+      </c>
+      <c r="D20" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" s="4" t="n">
+        <v>22.9</v>
+      </c>
+      <c r="F20" s="4" t="n">
         <v>2.4</v>
       </c>
-      <c r="F8" s="5" t="n">
-        <v>22.8</v>
-      </c>
-      <c r="G8" s="5" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="H8" s="5" t="n">
-        <v>107</v>
-      </c>
-      <c r="I8" s="5" t="n">
+      <c r="G20" s="4" t="n">
+        <v>248.2</v>
+      </c>
+      <c r="H20" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I20" s="4" t="n">
+        <v>225</v>
+      </c>
+      <c r="J20" s="4" t="inlineStr">
+        <is>
+          <t>主观诉求高·体检未印证</t>
+        </is>
+      </c>
+      <c r="K20" s="4" t="n"/>
+    </row>
+    <row r="21" ht="30" customHeight="1">
+      <c r="A21" s="4" t="n">
+        <v>19</v>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>大学路社区</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="n">
+        <v>97</v>
+      </c>
+      <c r="D21" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E21" s="4" t="n">
+        <v>45.4</v>
+      </c>
+      <c r="F21" s="4" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="G21" s="4" t="n">
+        <v>183.5</v>
+      </c>
+      <c r="H21" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="J8" s="7" t="inlineStr">
-        <is>
-          <t>客观隐患高
-诉求未暴露</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="5" t="n">
-        <v>7</v>
-      </c>
-      <c r="B9" s="6" t="inlineStr">
-        <is>
-          <t>西峡社区</t>
-        </is>
-      </c>
-      <c r="C9" s="5" t="n">
-        <v>78</v>
-      </c>
-      <c r="D9" s="5" t="n">
-        <v>105.1</v>
-      </c>
-      <c r="E9" s="5" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="F9" s="5" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="G9" s="5" t="n">
-        <v>41</v>
-      </c>
-      <c r="H9" s="5" t="n">
-        <v>91</v>
-      </c>
-      <c r="I9" s="5" t="n">
-        <v>35</v>
-      </c>
-      <c r="J9" s="7" t="inlineStr">
-        <is>
-          <t>客观隐患高
-诉求未暴露</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="5" t="n">
+      <c r="I21" s="4" t="n">
+        <v>222</v>
+      </c>
+      <c r="J21" s="4" t="inlineStr">
+        <is>
+          <t>主观诉求高·体检未印证</t>
+        </is>
+      </c>
+      <c r="K21" s="4" t="n"/>
+    </row>
+    <row r="22" ht="30" customHeight="1">
+      <c r="A22" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>伍临路社区</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="n">
+        <v>55</v>
+      </c>
+      <c r="D22" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" s="4" t="n">
+        <v>38.2</v>
+      </c>
+      <c r="F22" s="4" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="G22" s="4" t="n">
+        <v>363.6</v>
+      </c>
+      <c r="H22" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="B10" s="6" t="inlineStr">
-        <is>
-          <t>金安岭社区</t>
-        </is>
-      </c>
-      <c r="C10" s="5" t="n">
-        <v>56</v>
-      </c>
-      <c r="D10" s="5" t="n">
-        <v>130.4</v>
-      </c>
-      <c r="E10" s="5" t="n">
-        <v>16.1</v>
-      </c>
-      <c r="F10" s="5" t="n">
-        <v>19.6</v>
-      </c>
-      <c r="G10" s="5" t="n">
-        <v>19.6</v>
-      </c>
-      <c r="H10" s="5" t="n">
-        <v>84</v>
-      </c>
-      <c r="I10" s="5" t="n">
-        <v>20</v>
-      </c>
-      <c r="J10" s="7" t="inlineStr">
-        <is>
-          <t>客观隐患高
-诉求未暴露</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="5" t="n">
-        <v>9</v>
-      </c>
-      <c r="B11" s="6" t="inlineStr">
-        <is>
-          <t>镇境山社区</t>
-        </is>
-      </c>
-      <c r="C11" s="5" t="n">
-        <v>78</v>
-      </c>
-      <c r="D11" s="5" t="n">
-        <v>85.90000000000001</v>
-      </c>
-      <c r="E11" s="5" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="F11" s="5" t="n">
-        <v>19.2</v>
-      </c>
-      <c r="G11" s="5" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="H11" s="5" t="n">
-        <v>82</v>
-      </c>
-      <c r="I11" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="J11" s="7" t="inlineStr">
-        <is>
-          <t>客观隐患高
-诉求未暴露</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="5" t="n">
-        <v>10</v>
-      </c>
-      <c r="B12" s="6" t="inlineStr">
-        <is>
-          <t>幸福路社区</t>
-        </is>
-      </c>
-      <c r="C12" s="5" t="n">
-        <v>58</v>
-      </c>
-      <c r="D12" s="5" t="n">
-        <v>82.8</v>
-      </c>
-      <c r="E12" s="5" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="F12" s="5" t="n">
-        <v>29.3</v>
-      </c>
-      <c r="G12" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H12" s="5" t="n">
-        <v>65</v>
-      </c>
-      <c r="I12" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="J12" s="7" t="inlineStr">
-        <is>
-          <t>客观隐患高
-诉求未暴露</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="5" t="n">
-        <v>11</v>
-      </c>
-      <c r="B13" s="6" t="inlineStr">
-        <is>
-          <t>新隆康路社区</t>
-        </is>
-      </c>
-      <c r="C13" s="5" t="n">
-        <v>130</v>
-      </c>
-      <c r="D13" s="5" t="n">
-        <v>36.2</v>
-      </c>
-      <c r="E13" s="5" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="F13" s="5" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="G13" s="5" t="n">
-        <v>44.6</v>
-      </c>
-      <c r="H13" s="5" t="n">
-        <v>62</v>
-      </c>
-      <c r="I13" s="5" t="n">
-        <v>64</v>
-      </c>
-      <c r="J13" s="7" t="inlineStr">
-        <is>
-          <t>客观隐患高
-诉求未暴露</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="5" t="n">
-        <v>12</v>
-      </c>
-      <c r="B14" s="6" t="inlineStr">
-        <is>
-          <t>果园路社区</t>
-        </is>
-      </c>
-      <c r="C14" s="5" t="n">
-        <v>93</v>
-      </c>
-      <c r="D14" s="5" t="n">
-        <v>26.9</v>
-      </c>
-      <c r="E14" s="5" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="F14" s="5" t="n">
-        <v>28</v>
-      </c>
-      <c r="G14" s="5" t="n">
-        <v>66.7</v>
-      </c>
-      <c r="H14" s="5" t="n">
-        <v>51</v>
-      </c>
-      <c r="I14" s="5" t="n">
-        <v>73</v>
-      </c>
-      <c r="J14" s="7" t="inlineStr">
-        <is>
-          <t>客观隐患高
-诉求未暴露</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="5" t="n">
-        <v>13</v>
-      </c>
-      <c r="B15" s="6" t="inlineStr">
-        <is>
-          <t>桥北社区</t>
-        </is>
-      </c>
-      <c r="C15" s="5" t="n">
-        <v>48</v>
-      </c>
-      <c r="D15" s="5" t="n">
-        <v>35.4</v>
-      </c>
-      <c r="E15" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" s="5" t="n">
-        <v>41.7</v>
-      </c>
-      <c r="G15" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H15" s="5" t="n">
-        <v>37</v>
-      </c>
-      <c r="I15" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" s="7" t="inlineStr">
-        <is>
-          <t>客观隐患高
-诉求未暴露</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="8" t="n">
-        <v>14</v>
-      </c>
-      <c r="B16" s="9" t="inlineStr">
-        <is>
-          <t>朝阳路社区</t>
-        </is>
-      </c>
-      <c r="C16" s="8" t="n">
-        <v>84</v>
-      </c>
-      <c r="D16" s="8" t="n">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="E16" s="8" t="n">
-        <v>69</v>
-      </c>
-      <c r="F16" s="8" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="G16" s="8" t="n">
-        <v>638.1</v>
-      </c>
-      <c r="H16" s="8" t="n">
-        <v>11</v>
-      </c>
-      <c r="I16" s="8" t="n">
-        <v>594</v>
-      </c>
-      <c r="J16" s="10" t="inlineStr">
-        <is>
-          <t>主观诉求高
-体检未印证</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="8" t="n">
-        <v>15</v>
-      </c>
-      <c r="B17" s="9" t="inlineStr">
-        <is>
-          <t>万达社区</t>
-        </is>
-      </c>
-      <c r="C17" s="8" t="n">
-        <v>69</v>
-      </c>
-      <c r="D17" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="E17" s="8" t="n">
-        <v>72.5</v>
-      </c>
-      <c r="F17" s="8" t="n">
-        <v>10.1</v>
-      </c>
-      <c r="G17" s="8" t="n">
-        <v>653.6</v>
-      </c>
-      <c r="H17" s="8" t="n">
-        <v>7</v>
-      </c>
-      <c r="I17" s="8" t="n">
-        <v>501</v>
-      </c>
-      <c r="J17" s="10" t="inlineStr">
-        <is>
-          <t>主观诉求高
-体检未印证</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="8" t="n">
-        <v>16</v>
-      </c>
-      <c r="B18" s="9" t="inlineStr">
-        <is>
-          <t>港务社区</t>
-        </is>
-      </c>
-      <c r="C18" s="8" t="n">
-        <v>106</v>
-      </c>
-      <c r="D18" s="8" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="E18" s="8" t="n">
-        <v>78.3</v>
-      </c>
-      <c r="F18" s="8" t="n">
-        <v>14.2</v>
-      </c>
-      <c r="G18" s="8" t="n">
-        <v>315.1</v>
-      </c>
-      <c r="H18" s="8" t="n">
-        <v>17</v>
-      </c>
-      <c r="I18" s="8" t="n">
-        <v>417</v>
-      </c>
-      <c r="J18" s="10" t="inlineStr">
-        <is>
-          <t>主观诉求高
-体检未印证</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="8" t="n">
-        <v>17</v>
-      </c>
-      <c r="B19" s="9" t="inlineStr">
-        <is>
-          <t>建设社区</t>
-        </is>
-      </c>
-      <c r="C19" s="8" t="n">
-        <v>66</v>
-      </c>
-      <c r="D19" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="E19" s="8" t="n">
-        <v>78.8</v>
-      </c>
-      <c r="F19" s="8" t="n">
-        <v>13.6</v>
-      </c>
-      <c r="G19" s="8" t="n">
-        <v>484.8</v>
-      </c>
-      <c r="H19" s="8" t="n">
-        <v>9</v>
-      </c>
-      <c r="I19" s="8" t="n">
-        <v>372</v>
-      </c>
-      <c r="J19" s="10" t="inlineStr">
-        <is>
-          <t>主观诉求高
-体检未印证</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="8" t="n">
-        <v>18</v>
-      </c>
-      <c r="B20" s="9" t="inlineStr">
-        <is>
-          <t>岳湾路社区</t>
-        </is>
-      </c>
-      <c r="C20" s="8" t="n">
-        <v>83</v>
-      </c>
-      <c r="D20" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="E20" s="8" t="n">
-        <v>22.9</v>
-      </c>
-      <c r="F20" s="8" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="G20" s="8" t="n">
-        <v>248.2</v>
-      </c>
-      <c r="H20" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="I20" s="8" t="n">
-        <v>225</v>
-      </c>
-      <c r="J20" s="10" t="inlineStr">
-        <is>
-          <t>主观诉求高
-体检未印证</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="8" t="n">
-        <v>19</v>
-      </c>
-      <c r="B21" s="9" t="inlineStr">
-        <is>
-          <t>大学路社区</t>
-        </is>
-      </c>
-      <c r="C21" s="8" t="n">
-        <v>97</v>
-      </c>
-      <c r="D21" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="E21" s="8" t="n">
-        <v>45.4</v>
-      </c>
-      <c r="F21" s="8" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="G21" s="8" t="n">
-        <v>183.5</v>
-      </c>
-      <c r="H21" s="8" t="n">
-        <v>7</v>
-      </c>
-      <c r="I21" s="8" t="n">
-        <v>222</v>
-      </c>
-      <c r="J21" s="10" t="inlineStr">
-        <is>
-          <t>主观诉求高
-体检未印证</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="8" t="n">
-        <v>20</v>
-      </c>
-      <c r="B22" s="9" t="inlineStr">
-        <is>
-          <t>伍临路社区</t>
-        </is>
-      </c>
-      <c r="C22" s="8" t="n">
-        <v>55</v>
-      </c>
-      <c r="D22" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="E22" s="8" t="n">
-        <v>36.4</v>
-      </c>
-      <c r="F22" s="8" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="G22" s="8" t="n">
-        <v>365.5</v>
-      </c>
-      <c r="H22" s="8" t="n">
-        <v>8</v>
-      </c>
-      <c r="I22" s="8" t="n">
+      <c r="I22" s="4" t="n">
         <v>221</v>
       </c>
-      <c r="J22" s="10" t="inlineStr">
-        <is>
-          <t>主观诉求高
-体检未印证</t>
+      <c r="J22" s="4" t="inlineStr">
+        <is>
+          <t>主观诉求高·体检未印证</t>
+        </is>
+      </c>
+      <c r="K22" s="4" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>排序：双高 → 客观隐患高（按体检点降序）→ 主观诉求高（按诉求件数降序）；密度仅作资格与旁证，不作排序键。</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>脚注：体检高 = 客观隐患优先整治；诉求高 = 主观诉求集中须回应。两者都是行动对象、同属高优先，只是处置逻辑不同：一处隐患、一应诉求。</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="K1:K2"/>
+    <mergeCell ref="I1:I2"/>
+    <mergeCell ref="J1:J2"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="A1:A2"/>
+  </mergeCells>
+  <conditionalFormatting sqref="D3:D22">
+    <cfRule type="dataBar" priority="1">
+      <dataBar>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="700"/>
+        <color rgb="FF1F4E79"/>
+      </dataBar>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E3:E22">
+    <cfRule type="dataBar" priority="3">
+      <dataBar>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="700"/>
+        <color rgb="FFC55A11"/>
+      </dataBar>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F3:F22">
+    <cfRule type="dataBar" priority="2">
+      <dataBar>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="700"/>
+        <color rgb="FF1F4E79"/>
+      </dataBar>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G3:G22">
+    <cfRule type="dataBar" priority="4">
+      <dataBar>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="700"/>
+        <color rgb="FFC55A11"/>
+      </dataBar>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1406,237 +1564,237 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="7" t="inlineStr">
         <is>
           <t>序</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="7" t="inlineStr">
         <is>
           <t>社区</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="7" t="inlineStr">
         <is>
           <t>楼栋</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="7" t="inlineStr">
         <is>
           <t>体检问题（点）</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="7" t="inlineStr">
         <is>
           <t>市民诉求（件）</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" s="7" t="inlineStr">
         <is>
           <t>每百栋（体检/诉求）</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" s="7" t="inlineStr">
         <is>
           <t>综合评估</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="11" t="inlineStr">
+      <c r="A2" s="8" t="inlineStr">
         <is>
           <t>① 双高 · 体检+诉求都高（5 个）</t>
         </is>
       </c>
-      <c r="B2" s="12" t="n"/>
-      <c r="C2" s="12" t="n"/>
-      <c r="D2" s="12" t="n"/>
-      <c r="E2" s="12" t="n"/>
-      <c r="F2" s="12" t="n"/>
-      <c r="G2" s="12" t="n"/>
+      <c r="B2" s="9" t="n"/>
+      <c r="C2" s="9" t="n"/>
+      <c r="D2" s="9" t="n"/>
+      <c r="E2" s="9" t="n"/>
+      <c r="F2" s="9" t="n"/>
+      <c r="G2" s="9" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="n">
+      <c r="A3" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" s="11" t="inlineStr">
         <is>
           <t>营盘路社区</t>
         </is>
       </c>
-      <c r="C3" s="2" t="n">
+      <c r="C3" s="10" t="n">
         <v>66</v>
       </c>
-      <c r="D3" s="2" t="n">
+      <c r="D3" s="10" t="n">
         <v>37</v>
       </c>
-      <c r="E3" s="2" t="n">
+      <c r="E3" s="10" t="n">
         <v>117</v>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="F3" s="10" t="inlineStr">
         <is>
           <t>56.1 / 177.3</t>
         </is>
       </c>
-      <c r="G3" s="13" t="inlineStr">
+      <c r="G3" s="12" t="inlineStr">
         <is>
           <t>双高 ★</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="n">
+      <c r="A4" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" s="11" t="inlineStr">
         <is>
           <t>宝联社区</t>
         </is>
       </c>
-      <c r="C4" s="2" t="n">
+      <c r="C4" s="10" t="n">
         <v>94</v>
       </c>
-      <c r="D4" s="2" t="n">
+      <c r="D4" s="10" t="n">
         <v>29</v>
       </c>
-      <c r="E4" s="2" t="n">
+      <c r="E4" s="10" t="n">
         <v>156</v>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="F4" s="10" t="inlineStr">
         <is>
           <t>30.9 / 166.0</t>
         </is>
       </c>
-      <c r="G4" s="13" t="inlineStr">
+      <c r="G4" s="12" t="inlineStr">
         <is>
           <t>双高 ★</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="n">
+      <c r="A5" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B5" s="11" t="inlineStr">
         <is>
           <t>汕头路社区</t>
         </is>
       </c>
-      <c r="C5" s="2" t="n">
+      <c r="C5" s="10" t="n">
         <v>39</v>
       </c>
-      <c r="D5" s="2" t="n">
+      <c r="D5" s="10" t="n">
         <v>17</v>
       </c>
-      <c r="E5" s="2" t="n">
+      <c r="E5" s="10" t="n">
         <v>107</v>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F5" s="10" t="inlineStr">
         <is>
           <t>43.6 / 274.4</t>
         </is>
       </c>
-      <c r="G5" s="13" t="inlineStr">
+      <c r="G5" s="12" t="inlineStr">
         <is>
           <t>双高 ★</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="n">
+      <c r="A6" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B6" s="11" t="inlineStr">
         <is>
           <t>胜利四路社区</t>
         </is>
       </c>
-      <c r="C6" s="2" t="n">
+      <c r="C6" s="10" t="n">
         <v>44</v>
       </c>
-      <c r="D6" s="2" t="n">
+      <c r="D6" s="10" t="n">
         <v>16</v>
       </c>
-      <c r="E6" s="2" t="n">
+      <c r="E6" s="10" t="n">
         <v>115</v>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="F6" s="10" t="inlineStr">
         <is>
           <t>36.4 / 261.4</t>
         </is>
       </c>
-      <c r="G6" s="13" t="inlineStr">
+      <c r="G6" s="12" t="inlineStr">
         <is>
           <t>双高 ★</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="n">
+      <c r="A7" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B7" s="11" t="inlineStr">
         <is>
           <t>胜利二路社区</t>
         </is>
       </c>
-      <c r="C7" s="2" t="n">
+      <c r="C7" s="10" t="n">
         <v>30</v>
       </c>
-      <c r="D7" s="2" t="n">
+      <c r="D7" s="10" t="n">
         <v>9</v>
       </c>
-      <c r="E7" s="2" t="n">
+      <c r="E7" s="10" t="n">
         <v>111</v>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="F7" s="10" t="inlineStr">
         <is>
           <t>30.0 / 370.0</t>
         </is>
       </c>
-      <c r="G7" s="13" t="inlineStr">
+      <c r="G7" s="12" t="inlineStr">
         <is>
           <t>双高 ★</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="14" t="inlineStr">
+      <c r="A8" s="13" t="inlineStr">
         <is>
           <t>② 客观隐患高 · 体检独证（诉求未暴露 · 8 个）</t>
         </is>
       </c>
-      <c r="B8" s="15" t="n"/>
-      <c r="C8" s="15" t="n"/>
-      <c r="D8" s="15" t="n"/>
-      <c r="E8" s="15" t="n"/>
-      <c r="F8" s="15" t="n"/>
-      <c r="G8" s="15" t="n"/>
+      <c r="B8" s="14" t="n"/>
+      <c r="C8" s="14" t="n"/>
+      <c r="D8" s="14" t="n"/>
+      <c r="E8" s="14" t="n"/>
+      <c r="F8" s="14" t="n"/>
+      <c r="G8" s="14" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="n">
+      <c r="A9" s="15" t="n">
         <v>6</v>
       </c>
-      <c r="B9" s="6" t="inlineStr">
+      <c r="B9" s="16" t="inlineStr">
         <is>
           <t>深圳路社区</t>
         </is>
       </c>
-      <c r="C9" s="5" t="n">
+      <c r="C9" s="15" t="n">
         <v>127</v>
       </c>
-      <c r="D9" s="5" t="n">
+      <c r="D9" s="15" t="n">
         <v>107</v>
       </c>
-      <c r="E9" s="5" t="n">
+      <c r="E9" s="15" t="n">
         <v>7</v>
       </c>
-      <c r="F9" s="5" t="inlineStr">
+      <c r="F9" s="15" t="inlineStr">
         <is>
           <t>84.3 / 5.5</t>
         </is>
       </c>
-      <c r="G9" s="16" t="inlineStr">
+      <c r="G9" s="17" t="inlineStr">
         <is>
           <t>客观隐患高
 诉求未暴露</t>
@@ -1644,29 +1802,29 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="5" t="n">
+      <c r="A10" s="15" t="n">
         <v>7</v>
       </c>
-      <c r="B10" s="6" t="inlineStr">
+      <c r="B10" s="16" t="inlineStr">
         <is>
           <t>西峡社区</t>
         </is>
       </c>
-      <c r="C10" s="5" t="n">
+      <c r="C10" s="15" t="n">
         <v>78</v>
       </c>
-      <c r="D10" s="5" t="n">
+      <c r="D10" s="15" t="n">
         <v>91</v>
       </c>
-      <c r="E10" s="5" t="n">
+      <c r="E10" s="15" t="n">
         <v>35</v>
       </c>
-      <c r="F10" s="5" t="inlineStr">
+      <c r="F10" s="15" t="inlineStr">
         <is>
           <t>116.7 / 44.9</t>
         </is>
       </c>
-      <c r="G10" s="16" t="inlineStr">
+      <c r="G10" s="17" t="inlineStr">
         <is>
           <t>客观隐患高
 诉求未暴露</t>
@@ -1674,29 +1832,29 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="5" t="n">
+      <c r="A11" s="15" t="n">
         <v>8</v>
       </c>
-      <c r="B11" s="6" t="inlineStr">
+      <c r="B11" s="16" t="inlineStr">
         <is>
           <t>金安岭社区</t>
         </is>
       </c>
-      <c r="C11" s="5" t="n">
+      <c r="C11" s="15" t="n">
         <v>56</v>
       </c>
-      <c r="D11" s="5" t="n">
+      <c r="D11" s="15" t="n">
         <v>84</v>
       </c>
-      <c r="E11" s="5" t="n">
+      <c r="E11" s="15" t="n">
         <v>20</v>
       </c>
-      <c r="F11" s="5" t="inlineStr">
+      <c r="F11" s="15" t="inlineStr">
         <is>
           <t>150.0 / 35.7</t>
         </is>
       </c>
-      <c r="G11" s="16" t="inlineStr">
+      <c r="G11" s="17" t="inlineStr">
         <is>
           <t>客观隐患高
 诉求未暴露</t>
@@ -1704,29 +1862,29 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="5" t="n">
+      <c r="A12" s="15" t="n">
         <v>9</v>
       </c>
-      <c r="B12" s="6" t="inlineStr">
+      <c r="B12" s="16" t="inlineStr">
         <is>
           <t>镇境山社区</t>
         </is>
       </c>
-      <c r="C12" s="5" t="n">
+      <c r="C12" s="15" t="n">
         <v>78</v>
       </c>
-      <c r="D12" s="5" t="n">
+      <c r="D12" s="15" t="n">
         <v>82</v>
       </c>
-      <c r="E12" s="5" t="n">
+      <c r="E12" s="15" t="n">
         <v>5</v>
       </c>
-      <c r="F12" s="5" t="inlineStr">
+      <c r="F12" s="15" t="inlineStr">
         <is>
           <t>105.1 / 6.4</t>
         </is>
       </c>
-      <c r="G12" s="16" t="inlineStr">
+      <c r="G12" s="17" t="inlineStr">
         <is>
           <t>客观隐患高
 诉求未暴露</t>
@@ -1734,29 +1892,29 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="5" t="n">
+      <c r="A13" s="15" t="n">
         <v>10</v>
       </c>
-      <c r="B13" s="6" t="inlineStr">
+      <c r="B13" s="16" t="inlineStr">
         <is>
           <t>幸福路社区</t>
         </is>
       </c>
-      <c r="C13" s="5" t="n">
+      <c r="C13" s="15" t="n">
         <v>58</v>
       </c>
-      <c r="D13" s="5" t="n">
+      <c r="D13" s="15" t="n">
         <v>65</v>
       </c>
-      <c r="E13" s="5" t="n">
+      <c r="E13" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="F13" s="5" t="inlineStr">
+      <c r="F13" s="15" t="inlineStr">
         <is>
           <t>112.1 / 1.7</t>
         </is>
       </c>
-      <c r="G13" s="16" t="inlineStr">
+      <c r="G13" s="17" t="inlineStr">
         <is>
           <t>客观隐患高
 诉求未暴露</t>
@@ -1764,29 +1922,29 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="5" t="n">
+      <c r="A14" s="15" t="n">
         <v>11</v>
       </c>
-      <c r="B14" s="6" t="inlineStr">
+      <c r="B14" s="16" t="inlineStr">
         <is>
           <t>新隆康路社区</t>
         </is>
       </c>
-      <c r="C14" s="5" t="n">
+      <c r="C14" s="15" t="n">
         <v>130</v>
       </c>
-      <c r="D14" s="5" t="n">
+      <c r="D14" s="15" t="n">
         <v>62</v>
       </c>
-      <c r="E14" s="5" t="n">
+      <c r="E14" s="15" t="n">
         <v>64</v>
       </c>
-      <c r="F14" s="5" t="inlineStr">
+      <c r="F14" s="15" t="inlineStr">
         <is>
           <t>47.7 / 49.2</t>
         </is>
       </c>
-      <c r="G14" s="16" t="inlineStr">
+      <c r="G14" s="17" t="inlineStr">
         <is>
           <t>客观隐患高
 诉求未暴露</t>
@@ -1794,29 +1952,29 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="n">
+      <c r="A15" s="15" t="n">
         <v>12</v>
       </c>
-      <c r="B15" s="6" t="inlineStr">
+      <c r="B15" s="16" t="inlineStr">
         <is>
           <t>果园路社区</t>
         </is>
       </c>
-      <c r="C15" s="5" t="n">
+      <c r="C15" s="15" t="n">
         <v>93</v>
       </c>
-      <c r="D15" s="5" t="n">
+      <c r="D15" s="15" t="n">
         <v>51</v>
       </c>
-      <c r="E15" s="5" t="n">
+      <c r="E15" s="15" t="n">
         <v>73</v>
       </c>
-      <c r="F15" s="5" t="inlineStr">
+      <c r="F15" s="15" t="inlineStr">
         <is>
           <t>54.8 / 78.5</t>
         </is>
       </c>
-      <c r="G15" s="16" t="inlineStr">
+      <c r="G15" s="17" t="inlineStr">
         <is>
           <t>客观隐患高
 诉求未暴露</t>
@@ -1824,31 +1982,31 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="5" t="n">
+      <c r="A16" s="15" t="n">
         <v>13</v>
       </c>
-      <c r="B16" s="6" t="inlineStr">
+      <c r="B16" s="16" t="inlineStr">
         <is>
           <t>桥北社区</t>
         </is>
       </c>
-      <c r="C16" s="5" t="n">
+      <c r="C16" s="15" t="n">
         <v>48</v>
       </c>
-      <c r="D16" s="5" t="n">
+      <c r="D16" s="15" t="n">
         <v>37</v>
       </c>
-      <c r="E16" s="5" t="inlineStr">
+      <c r="E16" s="15" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F16" s="5" t="inlineStr">
+      <c r="F16" s="15" t="inlineStr">
         <is>
           <t>77.1 / —</t>
         </is>
       </c>
-      <c r="G16" s="16" t="inlineStr">
+      <c r="G16" s="17" t="inlineStr">
         <is>
           <t>客观隐患高
 诉求未暴露</t>
@@ -1856,42 +2014,42 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="17" t="inlineStr">
+      <c r="A17" s="18" t="inlineStr">
         <is>
           <t>③ 主观诉求高 · 热线独证（体检未印证 · 7 个）</t>
         </is>
       </c>
-      <c r="B17" s="18" t="n"/>
-      <c r="C17" s="18" t="n"/>
-      <c r="D17" s="18" t="n"/>
-      <c r="E17" s="18" t="n"/>
-      <c r="F17" s="18" t="n"/>
-      <c r="G17" s="18" t="n"/>
+      <c r="B17" s="19" t="n"/>
+      <c r="C17" s="19" t="n"/>
+      <c r="D17" s="19" t="n"/>
+      <c r="E17" s="19" t="n"/>
+      <c r="F17" s="19" t="n"/>
+      <c r="G17" s="19" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="8" t="n">
+      <c r="A18" s="20" t="n">
         <v>14</v>
       </c>
-      <c r="B18" s="9" t="inlineStr">
+      <c r="B18" s="21" t="inlineStr">
         <is>
           <t>朝阳路社区</t>
         </is>
       </c>
-      <c r="C18" s="8" t="n">
+      <c r="C18" s="20" t="n">
         <v>84</v>
       </c>
-      <c r="D18" s="8" t="n">
+      <c r="D18" s="20" t="n">
         <v>11</v>
       </c>
-      <c r="E18" s="8" t="n">
+      <c r="E18" s="20" t="n">
         <v>594</v>
       </c>
-      <c r="F18" s="8" t="inlineStr">
+      <c r="F18" s="20" t="inlineStr">
         <is>
           <t>13.1 / 707.1</t>
         </is>
       </c>
-      <c r="G18" s="19" t="inlineStr">
+      <c r="G18" s="22" t="inlineStr">
         <is>
           <t>主观诉求高
 体检未印证</t>
@@ -1899,29 +2057,29 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="8" t="n">
+      <c r="A19" s="20" t="n">
         <v>15</v>
       </c>
-      <c r="B19" s="9" t="inlineStr">
+      <c r="B19" s="21" t="inlineStr">
         <is>
           <t>万达社区</t>
         </is>
       </c>
-      <c r="C19" s="8" t="n">
+      <c r="C19" s="20" t="n">
         <v>69</v>
       </c>
-      <c r="D19" s="8" t="n">
+      <c r="D19" s="20" t="n">
         <v>7</v>
       </c>
-      <c r="E19" s="8" t="n">
+      <c r="E19" s="20" t="n">
         <v>501</v>
       </c>
-      <c r="F19" s="8" t="inlineStr">
+      <c r="F19" s="20" t="inlineStr">
         <is>
           <t>10.1 / 726.1</t>
         </is>
       </c>
-      <c r="G19" s="19" t="inlineStr">
+      <c r="G19" s="22" t="inlineStr">
         <is>
           <t>主观诉求高
 体检未印证</t>
@@ -1929,29 +2087,29 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="8" t="n">
+      <c r="A20" s="20" t="n">
         <v>16</v>
       </c>
-      <c r="B20" s="9" t="inlineStr">
+      <c r="B20" s="21" t="inlineStr">
         <is>
           <t>港务社区</t>
         </is>
       </c>
-      <c r="C20" s="8" t="n">
+      <c r="C20" s="20" t="n">
         <v>106</v>
       </c>
-      <c r="D20" s="8" t="n">
+      <c r="D20" s="20" t="n">
         <v>17</v>
       </c>
-      <c r="E20" s="8" t="n">
+      <c r="E20" s="20" t="n">
         <v>417</v>
       </c>
-      <c r="F20" s="8" t="inlineStr">
+      <c r="F20" s="20" t="inlineStr">
         <is>
           <t>16.0 / 393.4</t>
         </is>
       </c>
-      <c r="G20" s="19" t="inlineStr">
+      <c r="G20" s="22" t="inlineStr">
         <is>
           <t>主观诉求高
 体检未印证</t>
@@ -1959,29 +2117,29 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="8" t="n">
+      <c r="A21" s="20" t="n">
         <v>17</v>
       </c>
-      <c r="B21" s="9" t="inlineStr">
+      <c r="B21" s="21" t="inlineStr">
         <is>
           <t>建设社区</t>
         </is>
       </c>
-      <c r="C21" s="8" t="n">
+      <c r="C21" s="20" t="n">
         <v>66</v>
       </c>
-      <c r="D21" s="8" t="n">
+      <c r="D21" s="20" t="n">
         <v>9</v>
       </c>
-      <c r="E21" s="8" t="n">
+      <c r="E21" s="20" t="n">
         <v>372</v>
       </c>
-      <c r="F21" s="8" t="inlineStr">
+      <c r="F21" s="20" t="inlineStr">
         <is>
           <t>13.6 / 563.6</t>
         </is>
       </c>
-      <c r="G21" s="19" t="inlineStr">
+      <c r="G21" s="22" t="inlineStr">
         <is>
           <t>主观诉求高
 体检未印证</t>
@@ -1989,29 +2147,29 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="8" t="n">
+      <c r="A22" s="20" t="n">
         <v>18</v>
       </c>
-      <c r="B22" s="9" t="inlineStr">
+      <c r="B22" s="21" t="inlineStr">
         <is>
           <t>岳湾路社区</t>
         </is>
       </c>
-      <c r="C22" s="8" t="n">
+      <c r="C22" s="20" t="n">
         <v>83</v>
       </c>
-      <c r="D22" s="8" t="n">
+      <c r="D22" s="20" t="n">
         <v>2</v>
       </c>
-      <c r="E22" s="8" t="n">
+      <c r="E22" s="20" t="n">
         <v>225</v>
       </c>
-      <c r="F22" s="8" t="inlineStr">
+      <c r="F22" s="20" t="inlineStr">
         <is>
           <t>2.4 / 271.1</t>
         </is>
       </c>
-      <c r="G22" s="19" t="inlineStr">
+      <c r="G22" s="22" t="inlineStr">
         <is>
           <t>主观诉求高
 体检未印证</t>
@@ -2019,29 +2177,29 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="8" t="n">
+      <c r="A23" s="20" t="n">
         <v>19</v>
       </c>
-      <c r="B23" s="9" t="inlineStr">
+      <c r="B23" s="21" t="inlineStr">
         <is>
           <t>大学路社区</t>
         </is>
       </c>
-      <c r="C23" s="8" t="n">
+      <c r="C23" s="20" t="n">
         <v>97</v>
       </c>
-      <c r="D23" s="8" t="n">
+      <c r="D23" s="20" t="n">
         <v>7</v>
       </c>
-      <c r="E23" s="8" t="n">
+      <c r="E23" s="20" t="n">
         <v>222</v>
       </c>
-      <c r="F23" s="8" t="inlineStr">
+      <c r="F23" s="20" t="inlineStr">
         <is>
           <t>7.2 / 228.9</t>
         </is>
       </c>
-      <c r="G23" s="19" t="inlineStr">
+      <c r="G23" s="22" t="inlineStr">
         <is>
           <t>主观诉求高
 体检未印证</t>
@@ -2049,29 +2207,29 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="8" t="n">
+      <c r="A24" s="20" t="n">
         <v>20</v>
       </c>
-      <c r="B24" s="9" t="inlineStr">
+      <c r="B24" s="21" t="inlineStr">
         <is>
           <t>伍临路社区</t>
         </is>
       </c>
-      <c r="C24" s="8" t="n">
+      <c r="C24" s="20" t="n">
         <v>55</v>
       </c>
-      <c r="D24" s="8" t="n">
+      <c r="D24" s="20" t="n">
         <v>8</v>
       </c>
-      <c r="E24" s="8" t="n">
+      <c r="E24" s="20" t="n">
         <v>221</v>
       </c>
-      <c r="F24" s="8" t="inlineStr">
+      <c r="F24" s="20" t="inlineStr">
         <is>
           <t>14.5 / 401.8</t>
         </is>
       </c>
-      <c r="G24" s="19" t="inlineStr">
+      <c r="G24" s="22" t="inlineStr">
         <is>
           <t>主观诉求高
 体检未印证</t>
@@ -2094,236 +2252,212 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F27"/>
+  <dimension ref="A1:F24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
-    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
     <col width="7" customWidth="1" min="3" max="3"/>
-    <col width="26" customWidth="1" min="4" max="4"/>
-    <col width="26" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
     <col width="18" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>序</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>社区</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="A1" s="7" t="inlineStr">
+        <is>
+          <t>序号</t>
+        </is>
+      </c>
+      <c r="B1" s="7" t="inlineStr">
+        <is>
+          <t>名称</t>
+        </is>
+      </c>
+      <c r="C1" s="7" t="inlineStr">
         <is>
           <t>楼栋</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>体检（点·每百栋）</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>诉求（件·每百栋）</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>综合评估</t>
+      <c r="D1" s="7" t="inlineStr">
+        <is>
+          <t>体检（每百栋）</t>
+        </is>
+      </c>
+      <c r="E1" s="7" t="inlineStr">
+        <is>
+          <t>诉求（每百栋）</t>
+        </is>
+      </c>
+      <c r="F1" s="7" t="inlineStr">
+        <is>
+          <t>评估</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="11" t="inlineStr">
+      <c r="A2" s="8" t="inlineStr">
         <is>
           <t>① 双高 · 体检+诉求都高（5 个）</t>
         </is>
       </c>
-      <c r="B2" s="12" t="n"/>
-      <c r="C2" s="12" t="n"/>
-      <c r="D2" s="12" t="n"/>
-      <c r="E2" s="12" t="n"/>
-      <c r="F2" s="12" t="n"/>
+      <c r="B2" s="9" t="n"/>
+      <c r="C2" s="9" t="n"/>
+      <c r="D2" s="9" t="n"/>
+      <c r="E2" s="9" t="n"/>
+      <c r="F2" s="9" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="n">
+      <c r="A3" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" s="11" t="inlineStr">
         <is>
           <t>营盘路社区</t>
         </is>
       </c>
-      <c r="C3" s="2" t="n">
+      <c r="C3" s="10" t="n">
         <v>66</v>
       </c>
-      <c r="D3" s="20" t="inlineStr">
-        <is>
-          <t>████████ 37</t>
-        </is>
-      </c>
-      <c r="E3" s="21" t="inlineStr">
-        <is>
-          <t>█████ 117</t>
-        </is>
-      </c>
-      <c r="F3" s="13" t="inlineStr">
+      <c r="D3" s="10" t="n">
+        <v>56.1</v>
+      </c>
+      <c r="E3" s="10" t="n">
+        <v>177.3</v>
+      </c>
+      <c r="F3" s="12" t="inlineStr">
         <is>
           <t>双高 ★</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="n">
+      <c r="A4" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" s="11" t="inlineStr">
         <is>
           <t>宝联社区</t>
         </is>
       </c>
-      <c r="C4" s="2" t="n">
+      <c r="C4" s="10" t="n">
         <v>94</v>
       </c>
-      <c r="D4" s="20" t="inlineStr">
-        <is>
-          <t>█████ 29</t>
-        </is>
-      </c>
-      <c r="E4" s="21" t="inlineStr">
-        <is>
-          <t>█████ 156</t>
-        </is>
-      </c>
-      <c r="F4" s="13" t="inlineStr">
+      <c r="D4" s="10" t="n">
+        <v>30.9</v>
+      </c>
+      <c r="E4" s="10" t="n">
+        <v>166</v>
+      </c>
+      <c r="F4" s="12" t="inlineStr">
         <is>
           <t>双高 ★</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="n">
+      <c r="A5" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B5" s="11" t="inlineStr">
         <is>
           <t>汕头路社区</t>
         </is>
       </c>
-      <c r="C5" s="2" t="n">
+      <c r="C5" s="10" t="n">
         <v>39</v>
       </c>
-      <c r="D5" s="20" t="inlineStr">
-        <is>
-          <t>██████ 17</t>
-        </is>
-      </c>
-      <c r="E5" s="21" t="inlineStr">
-        <is>
-          <t>████████ 107</t>
-        </is>
-      </c>
-      <c r="F5" s="13" t="inlineStr">
+      <c r="D5" s="10" t="n">
+        <v>43.6</v>
+      </c>
+      <c r="E5" s="10" t="n">
+        <v>274.4</v>
+      </c>
+      <c r="F5" s="12" t="inlineStr">
         <is>
           <t>双高 ★</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="n">
+      <c r="A6" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B6" s="11" t="inlineStr">
         <is>
           <t>胜利四路社区</t>
         </is>
       </c>
-      <c r="C6" s="2" t="n">
+      <c r="C6" s="10" t="n">
         <v>44</v>
       </c>
-      <c r="D6" s="20" t="inlineStr">
-        <is>
-          <t>█████ 16</t>
-        </is>
-      </c>
-      <c r="E6" s="21" t="inlineStr">
-        <is>
-          <t>████████ 115</t>
-        </is>
-      </c>
-      <c r="F6" s="13" t="inlineStr">
+      <c r="D6" s="10" t="n">
+        <v>36.4</v>
+      </c>
+      <c r="E6" s="10" t="n">
+        <v>261.4</v>
+      </c>
+      <c r="F6" s="12" t="inlineStr">
         <is>
           <t>双高 ★</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="n">
+      <c r="A7" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B7" s="11" t="inlineStr">
         <is>
           <t>胜利二路社区</t>
         </is>
       </c>
-      <c r="C7" s="2" t="n">
+      <c r="C7" s="10" t="n">
         <v>30</v>
       </c>
-      <c r="D7" s="20" t="inlineStr">
-        <is>
-          <t>████ 9</t>
-        </is>
-      </c>
-      <c r="E7" s="21" t="inlineStr">
-        <is>
-          <t>███████████ 111</t>
-        </is>
-      </c>
-      <c r="F7" s="13" t="inlineStr">
+      <c r="D7" s="10" t="n">
+        <v>30</v>
+      </c>
+      <c r="E7" s="10" t="n">
+        <v>370</v>
+      </c>
+      <c r="F7" s="12" t="inlineStr">
         <is>
           <t>双高 ★</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="14" t="inlineStr">
+      <c r="A8" s="13" t="inlineStr">
         <is>
           <t>② 客观隐患高 · 体检独证（诉求未暴露 · 8 个）</t>
         </is>
       </c>
-      <c r="B8" s="15" t="n"/>
-      <c r="C8" s="15" t="n"/>
-      <c r="D8" s="15" t="n"/>
-      <c r="E8" s="15" t="n"/>
-      <c r="F8" s="15" t="n"/>
+      <c r="B8" s="14" t="n"/>
+      <c r="C8" s="14" t="n"/>
+      <c r="D8" s="14" t="n"/>
+      <c r="E8" s="14" t="n"/>
+      <c r="F8" s="14" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="n">
+      <c r="A9" s="15" t="n">
         <v>6</v>
       </c>
-      <c r="B9" s="6" t="inlineStr">
+      <c r="B9" s="16" t="inlineStr">
         <is>
           <t>深圳路社区</t>
         </is>
       </c>
-      <c r="C9" s="5" t="n">
+      <c r="C9" s="15" t="n">
         <v>127</v>
       </c>
-      <c r="D9" s="22" t="inlineStr">
-        <is>
-          <t>████████████ 107</t>
-        </is>
-      </c>
-      <c r="E9" s="23" t="inlineStr">
-        <is>
-          <t>█ 7</t>
-        </is>
-      </c>
-      <c r="F9" s="16" t="inlineStr">
+      <c r="D9" s="15" t="n">
+        <v>84.3</v>
+      </c>
+      <c r="E9" s="15" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="F9" s="17" t="inlineStr">
         <is>
           <t>客观隐患高
 诉求未暴露</t>
@@ -2331,28 +2465,24 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="5" t="n">
+      <c r="A10" s="15" t="n">
         <v>7</v>
       </c>
-      <c r="B10" s="6" t="inlineStr">
+      <c r="B10" s="16" t="inlineStr">
         <is>
           <t>西峡社区</t>
         </is>
       </c>
-      <c r="C10" s="5" t="n">
+      <c r="C10" s="15" t="n">
         <v>78</v>
       </c>
-      <c r="D10" s="22" t="inlineStr">
-        <is>
-          <t>█████████████████ 91</t>
-        </is>
-      </c>
-      <c r="E10" s="23" t="inlineStr">
-        <is>
-          <t>█ 35</t>
-        </is>
-      </c>
-      <c r="F10" s="16" t="inlineStr">
+      <c r="D10" s="15" t="n">
+        <v>116.7</v>
+      </c>
+      <c r="E10" s="15" t="n">
+        <v>44.9</v>
+      </c>
+      <c r="F10" s="17" t="inlineStr">
         <is>
           <t>客观隐患高
 诉求未暴露</t>
@@ -2360,28 +2490,24 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="5" t="n">
+      <c r="A11" s="15" t="n">
         <v>8</v>
       </c>
-      <c r="B11" s="6" t="inlineStr">
+      <c r="B11" s="16" t="inlineStr">
         <is>
           <t>金安岭社区</t>
         </is>
       </c>
-      <c r="C11" s="5" t="n">
+      <c r="C11" s="15" t="n">
         <v>56</v>
       </c>
-      <c r="D11" s="22" t="inlineStr">
-        <is>
-          <t>██████████████████████ 84</t>
-        </is>
-      </c>
-      <c r="E11" s="23" t="inlineStr">
-        <is>
-          <t>█ 20</t>
-        </is>
-      </c>
-      <c r="F11" s="16" t="inlineStr">
+      <c r="D11" s="15" t="n">
+        <v>150</v>
+      </c>
+      <c r="E11" s="15" t="n">
+        <v>35.7</v>
+      </c>
+      <c r="F11" s="17" t="inlineStr">
         <is>
           <t>客观隐患高
 诉求未暴露</t>
@@ -2389,28 +2515,24 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="5" t="n">
+      <c r="A12" s="15" t="n">
         <v>9</v>
       </c>
-      <c r="B12" s="6" t="inlineStr">
+      <c r="B12" s="16" t="inlineStr">
         <is>
           <t>镇境山社区</t>
         </is>
       </c>
-      <c r="C12" s="5" t="n">
+      <c r="C12" s="15" t="n">
         <v>78</v>
       </c>
-      <c r="D12" s="22" t="inlineStr">
-        <is>
-          <t>███████████████ 82</t>
-        </is>
-      </c>
-      <c r="E12" s="23" t="inlineStr">
-        <is>
-          <t>█ 5</t>
-        </is>
-      </c>
-      <c r="F12" s="16" t="inlineStr">
+      <c r="D12" s="15" t="n">
+        <v>105.1</v>
+      </c>
+      <c r="E12" s="15" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="F12" s="17" t="inlineStr">
         <is>
           <t>客观隐患高
 诉求未暴露</t>
@@ -2418,28 +2540,24 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="5" t="n">
+      <c r="A13" s="15" t="n">
         <v>10</v>
       </c>
-      <c r="B13" s="6" t="inlineStr">
+      <c r="B13" s="16" t="inlineStr">
         <is>
           <t>幸福路社区</t>
         </is>
       </c>
-      <c r="C13" s="5" t="n">
+      <c r="C13" s="15" t="n">
         <v>58</v>
       </c>
-      <c r="D13" s="22" t="inlineStr">
-        <is>
-          <t>████████████████ 65</t>
-        </is>
-      </c>
-      <c r="E13" s="23" t="inlineStr">
-        <is>
-          <t>█ 1</t>
-        </is>
-      </c>
-      <c r="F13" s="16" t="inlineStr">
+      <c r="D13" s="15" t="n">
+        <v>112.1</v>
+      </c>
+      <c r="E13" s="15" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="F13" s="17" t="inlineStr">
         <is>
           <t>客观隐患高
 诉求未暴露</t>
@@ -2447,28 +2565,24 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="5" t="n">
+      <c r="A14" s="15" t="n">
         <v>11</v>
       </c>
-      <c r="B14" s="6" t="inlineStr">
+      <c r="B14" s="16" t="inlineStr">
         <is>
           <t>新隆康路社区</t>
         </is>
       </c>
-      <c r="C14" s="5" t="n">
+      <c r="C14" s="15" t="n">
         <v>130</v>
       </c>
-      <c r="D14" s="22" t="inlineStr">
-        <is>
-          <t>███████ 62</t>
-        </is>
-      </c>
-      <c r="E14" s="23" t="inlineStr">
-        <is>
-          <t>█ 64</t>
-        </is>
-      </c>
-      <c r="F14" s="16" t="inlineStr">
+      <c r="D14" s="15" t="n">
+        <v>47.7</v>
+      </c>
+      <c r="E14" s="15" t="n">
+        <v>49.2</v>
+      </c>
+      <c r="F14" s="17" t="inlineStr">
         <is>
           <t>客观隐患高
 诉求未暴露</t>
@@ -2476,28 +2590,24 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="n">
+      <c r="A15" s="15" t="n">
         <v>12</v>
       </c>
-      <c r="B15" s="6" t="inlineStr">
+      <c r="B15" s="16" t="inlineStr">
         <is>
           <t>果园路社区</t>
         </is>
       </c>
-      <c r="C15" s="5" t="n">
+      <c r="C15" s="15" t="n">
         <v>93</v>
       </c>
-      <c r="D15" s="22" t="inlineStr">
-        <is>
-          <t>████████ 51</t>
-        </is>
-      </c>
-      <c r="E15" s="23" t="inlineStr">
-        <is>
-          <t>██ 73</t>
-        </is>
-      </c>
-      <c r="F15" s="16" t="inlineStr">
+      <c r="D15" s="15" t="n">
+        <v>54.8</v>
+      </c>
+      <c r="E15" s="15" t="n">
+        <v>78.5</v>
+      </c>
+      <c r="F15" s="17" t="inlineStr">
         <is>
           <t>客观隐患高
 诉求未暴露</t>
@@ -2505,28 +2615,24 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="5" t="n">
+      <c r="A16" s="15" t="n">
         <v>13</v>
       </c>
-      <c r="B16" s="6" t="inlineStr">
+      <c r="B16" s="16" t="inlineStr">
         <is>
           <t>桥北社区</t>
         </is>
       </c>
-      <c r="C16" s="5" t="n">
+      <c r="C16" s="15" t="n">
         <v>48</v>
       </c>
-      <c r="D16" s="22" t="inlineStr">
-        <is>
-          <t>███████████ 37</t>
-        </is>
-      </c>
-      <c r="E16" s="23" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F16" s="16" t="inlineStr">
+      <c r="D16" s="15" t="n">
+        <v>77.09999999999999</v>
+      </c>
+      <c r="E16" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" s="17" t="inlineStr">
         <is>
           <t>客观隐患高
 诉求未暴露</t>
@@ -2534,40 +2640,36 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="17" t="inlineStr">
+      <c r="A17" s="18" t="inlineStr">
         <is>
           <t>③ 主观诉求高 · 热线独证（体检未印证 · 7 个）</t>
         </is>
       </c>
-      <c r="B17" s="18" t="n"/>
-      <c r="C17" s="18" t="n"/>
-      <c r="D17" s="18" t="n"/>
-      <c r="E17" s="18" t="n"/>
-      <c r="F17" s="18" t="n"/>
+      <c r="B17" s="19" t="n"/>
+      <c r="C17" s="19" t="n"/>
+      <c r="D17" s="19" t="n"/>
+      <c r="E17" s="19" t="n"/>
+      <c r="F17" s="19" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="8" t="n">
+      <c r="A18" s="20" t="n">
         <v>14</v>
       </c>
-      <c r="B18" s="9" t="inlineStr">
+      <c r="B18" s="21" t="inlineStr">
         <is>
           <t>朝阳路社区</t>
         </is>
       </c>
-      <c r="C18" s="8" t="n">
+      <c r="C18" s="20" t="n">
         <v>84</v>
       </c>
-      <c r="D18" s="24" t="inlineStr">
-        <is>
-          <t>██ 11</t>
-        </is>
-      </c>
-      <c r="E18" s="25" t="inlineStr">
-        <is>
-          <t>█████████████████████ 594</t>
-        </is>
-      </c>
-      <c r="F18" s="19" t="inlineStr">
+      <c r="D18" s="20" t="n">
+        <v>13.1</v>
+      </c>
+      <c r="E18" s="20" t="n">
+        <v>707.1</v>
+      </c>
+      <c r="F18" s="22" t="inlineStr">
         <is>
           <t>主观诉求高
 体检未印证</t>
@@ -2575,28 +2677,24 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="8" t="n">
+      <c r="A19" s="20" t="n">
         <v>15</v>
       </c>
-      <c r="B19" s="9" t="inlineStr">
+      <c r="B19" s="21" t="inlineStr">
         <is>
           <t>万达社区</t>
         </is>
       </c>
-      <c r="C19" s="8" t="n">
+      <c r="C19" s="20" t="n">
         <v>69</v>
       </c>
-      <c r="D19" s="24" t="inlineStr">
-        <is>
-          <t>█ 7</t>
-        </is>
-      </c>
-      <c r="E19" s="25" t="inlineStr">
-        <is>
-          <t>██████████████████████ 501</t>
-        </is>
-      </c>
-      <c r="F19" s="19" t="inlineStr">
+      <c r="D19" s="20" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="E19" s="20" t="n">
+        <v>726.1</v>
+      </c>
+      <c r="F19" s="22" t="inlineStr">
         <is>
           <t>主观诉求高
 体检未印证</t>
@@ -2604,28 +2702,24 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="8" t="n">
+      <c r="A20" s="20" t="n">
         <v>16</v>
       </c>
-      <c r="B20" s="9" t="inlineStr">
+      <c r="B20" s="21" t="inlineStr">
         <is>
           <t>港务社区</t>
         </is>
       </c>
-      <c r="C20" s="8" t="n">
+      <c r="C20" s="20" t="n">
         <v>106</v>
       </c>
-      <c r="D20" s="24" t="inlineStr">
-        <is>
-          <t>██ 17</t>
-        </is>
-      </c>
-      <c r="E20" s="25" t="inlineStr">
-        <is>
-          <t>████████████ 417</t>
-        </is>
-      </c>
-      <c r="F20" s="19" t="inlineStr">
+      <c r="D20" s="20" t="n">
+        <v>16</v>
+      </c>
+      <c r="E20" s="20" t="n">
+        <v>393.4</v>
+      </c>
+      <c r="F20" s="22" t="inlineStr">
         <is>
           <t>主观诉求高
 体检未印证</t>
@@ -2633,28 +2727,24 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="8" t="n">
+      <c r="A21" s="20" t="n">
         <v>17</v>
       </c>
-      <c r="B21" s="9" t="inlineStr">
+      <c r="B21" s="21" t="inlineStr">
         <is>
           <t>建设社区</t>
         </is>
       </c>
-      <c r="C21" s="8" t="n">
+      <c r="C21" s="20" t="n">
         <v>66</v>
       </c>
-      <c r="D21" s="24" t="inlineStr">
-        <is>
-          <t>██ 9</t>
-        </is>
-      </c>
-      <c r="E21" s="25" t="inlineStr">
-        <is>
-          <t>█████████████████ 372</t>
-        </is>
-      </c>
-      <c r="F21" s="19" t="inlineStr">
+      <c r="D21" s="20" t="n">
+        <v>13.6</v>
+      </c>
+      <c r="E21" s="20" t="n">
+        <v>563.6</v>
+      </c>
+      <c r="F21" s="22" t="inlineStr">
         <is>
           <t>主观诉求高
 体检未印证</t>
@@ -2662,28 +2752,24 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="8" t="n">
+      <c r="A22" s="20" t="n">
         <v>18</v>
       </c>
-      <c r="B22" s="9" t="inlineStr">
+      <c r="B22" s="21" t="inlineStr">
         <is>
           <t>岳湾路社区</t>
         </is>
       </c>
-      <c r="C22" s="8" t="n">
+      <c r="C22" s="20" t="n">
         <v>83</v>
       </c>
-      <c r="D22" s="24" t="inlineStr">
-        <is>
-          <t>█ 2</t>
-        </is>
-      </c>
-      <c r="E22" s="25" t="inlineStr">
-        <is>
-          <t>████████ 225</t>
-        </is>
-      </c>
-      <c r="F22" s="19" t="inlineStr">
+      <c r="D22" s="20" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="E22" s="20" t="n">
+        <v>271.1</v>
+      </c>
+      <c r="F22" s="22" t="inlineStr">
         <is>
           <t>主观诉求高
 体检未印证</t>
@@ -2691,28 +2777,24 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="8" t="n">
+      <c r="A23" s="20" t="n">
         <v>19</v>
       </c>
-      <c r="B23" s="9" t="inlineStr">
+      <c r="B23" s="21" t="inlineStr">
         <is>
           <t>大学路社区</t>
         </is>
       </c>
-      <c r="C23" s="8" t="n">
+      <c r="C23" s="20" t="n">
         <v>97</v>
       </c>
-      <c r="D23" s="24" t="inlineStr">
-        <is>
-          <t>█ 7</t>
-        </is>
-      </c>
-      <c r="E23" s="25" t="inlineStr">
-        <is>
-          <t>███████ 222</t>
-        </is>
-      </c>
-      <c r="F23" s="19" t="inlineStr">
+      <c r="D23" s="20" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="E23" s="20" t="n">
+        <v>228.9</v>
+      </c>
+      <c r="F23" s="22" t="inlineStr">
         <is>
           <t>主观诉求高
 体检未印证</t>
@@ -2720,56 +2802,54 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="8" t="n">
+      <c r="A24" s="20" t="n">
         <v>20</v>
       </c>
-      <c r="B24" s="9" t="inlineStr">
+      <c r="B24" s="21" t="inlineStr">
         <is>
           <t>伍临路社区</t>
         </is>
       </c>
-      <c r="C24" s="8" t="n">
+      <c r="C24" s="20" t="n">
         <v>55</v>
       </c>
-      <c r="D24" s="24" t="inlineStr">
-        <is>
-          <t>██ 8</t>
-        </is>
-      </c>
-      <c r="E24" s="25" t="inlineStr">
-        <is>
-          <t>████████████ 221</t>
-        </is>
-      </c>
-      <c r="F24" s="19" t="inlineStr">
+      <c r="D24" s="20" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="E24" s="20" t="n">
+        <v>401.8</v>
+      </c>
+      <c r="F24" s="22" t="inlineStr">
         <is>
           <t>主观诉求高
 体检未印证</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="26" t="inlineStr">
-        <is>
-          <t>横条 = 每百栋密度（体检满格 150 点/百栋、诉求满格 726 件/百栋·两轨分刻度）；条后数字 = 绝对量（体检点 / 诉求件）。</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="26" t="inlineStr">
-        <is>
-          <t>体检 = 体检安全 + 体检民生；诉求 = 12345 九类（安全 4 + 民生 5·剔「其他」）；「—」= 无隐患/无诉求。</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="3">
+    <mergeCell ref="A8:F8"/>
     <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A27:F27"/>
-    <mergeCell ref="A8:F8"/>
     <mergeCell ref="A17:F17"/>
-    <mergeCell ref="A26:F26"/>
   </mergeCells>
+  <conditionalFormatting sqref="D3:D24">
+    <cfRule type="dataBar" priority="1">
+      <dataBar gradient="0" showValue="1">
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="700"/>
+        <color rgb="001F4E79"/>
+      </dataBar>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E3:E24">
+    <cfRule type="dataBar" priority="2">
+      <dataBar gradient="0" showValue="1">
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="700"/>
+        <color rgb="00C55A11"/>
+      </dataBar>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/DATA/analysis/page7小结/page7_分组汇总_2026-08-14_最终.xlsx
+++ b/DATA/analysis/page7小结/page7_分组汇总_2026-08-14_最终.xlsx
@@ -358,6 +358,21 @@
 </styleSheet>
 </file>
 
+<file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>Codex</author>
+  </authors>
+  <commentList>
+    <comment ref="A1" authorId="0" shapeId="0">
+      <text>
+        <t>内部注（不对外）：作图实际社区面数=体检对象西陵+伍家岗全集(约130面)，统计底数=120(体检报告)；明面统一按120、图表对应。</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -2851,5 +2866,6 @@
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
--- a/DATA/analysis/page7小结/page7_分组汇总_2026-08-14_最终.xlsx
+++ b/DATA/analysis/page7小结/page7_分组汇总_2026-08-14_最终.xlsx
@@ -2851,7 +2851,7 @@
     <cfRule type="dataBar" priority="1">
       <dataBar gradient="0" showValue="1">
         <cfvo type="num" val="0"/>
-        <cfvo type="num" val="700"/>
+        <cfvo type="num" val="150"/>
         <color rgb="001F4E79"/>
       </dataBar>
     </cfRule>
@@ -2860,7 +2860,7 @@
     <cfRule type="dataBar" priority="2">
       <dataBar gradient="0" showValue="1">
         <cfvo type="num" val="0"/>
-        <cfvo type="num" val="700"/>
+        <cfvo type="num" val="726"/>
         <color rgb="00C55A11"/>
       </dataBar>
     </cfRule>

--- a/DATA/analysis/page7小结/page7_分组汇总_2026-08-14_最终.xlsx
+++ b/DATA/analysis/page7小结/page7_分组汇总_2026-08-14_最终.xlsx
@@ -1618,7 +1618,7 @@
     <row r="2">
       <c r="A2" s="8" t="inlineStr">
         <is>
-          <t>① 双高 · 体检+诉求都高（5 个）</t>
+          <t>① 双高（体检问题+群众诉求 · 5 个社区）</t>
         </is>
       </c>
       <c r="B2" s="9" t="n"/>
@@ -1653,7 +1653,7 @@
       </c>
       <c r="G3" s="12" t="inlineStr">
         <is>
-          <t>双高 ★</t>
+          <t>双高</t>
         </is>
       </c>
     </row>
@@ -1682,7 +1682,7 @@
       </c>
       <c r="G4" s="12" t="inlineStr">
         <is>
-          <t>双高 ★</t>
+          <t>双高</t>
         </is>
       </c>
     </row>
@@ -1711,7 +1711,7 @@
       </c>
       <c r="G5" s="12" t="inlineStr">
         <is>
-          <t>双高 ★</t>
+          <t>双高</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="G6" s="12" t="inlineStr">
         <is>
-          <t>双高 ★</t>
+          <t>双高</t>
         </is>
       </c>
     </row>
@@ -1769,14 +1769,14 @@
       </c>
       <c r="G7" s="12" t="inlineStr">
         <is>
-          <t>双高 ★</t>
+          <t>双高</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="13" t="inlineStr">
         <is>
-          <t>② 客观隐患高 · 体检独证（诉求未暴露 · 8 个）</t>
+          <t>② 问题指标高（诉求未反映 · 8 个社区）</t>
         </is>
       </c>
       <c r="B8" s="14" t="n"/>
@@ -1811,8 +1811,7 @@
       </c>
       <c r="G9" s="17" t="inlineStr">
         <is>
-          <t>客观隐患高
-诉求未暴露</t>
+          <t>体检问题指标较高</t>
         </is>
       </c>
     </row>
@@ -1841,8 +1840,7 @@
       </c>
       <c r="G10" s="17" t="inlineStr">
         <is>
-          <t>客观隐患高
-诉求未暴露</t>
+          <t>体检问题指标较高</t>
         </is>
       </c>
     </row>
@@ -1871,8 +1869,7 @@
       </c>
       <c r="G11" s="17" t="inlineStr">
         <is>
-          <t>客观隐患高
-诉求未暴露</t>
+          <t>体检问题指标较高</t>
         </is>
       </c>
     </row>
@@ -1901,8 +1898,7 @@
       </c>
       <c r="G12" s="17" t="inlineStr">
         <is>
-          <t>客观隐患高
-诉求未暴露</t>
+          <t>体检问题指标较高</t>
         </is>
       </c>
     </row>
@@ -1931,8 +1927,7 @@
       </c>
       <c r="G13" s="17" t="inlineStr">
         <is>
-          <t>客观隐患高
-诉求未暴露</t>
+          <t>体检问题指标较高</t>
         </is>
       </c>
     </row>
@@ -1961,8 +1956,7 @@
       </c>
       <c r="G14" s="17" t="inlineStr">
         <is>
-          <t>客观隐患高
-诉求未暴露</t>
+          <t>体检问题指标较高</t>
         </is>
       </c>
     </row>
@@ -1991,8 +1985,7 @@
       </c>
       <c r="G15" s="17" t="inlineStr">
         <is>
-          <t>客观隐患高
-诉求未暴露</t>
+          <t>体检问题指标较高</t>
         </is>
       </c>
     </row>
@@ -2023,15 +2016,14 @@
       </c>
       <c r="G16" s="17" t="inlineStr">
         <is>
-          <t>客观隐患高
-诉求未暴露</t>
+          <t>体检问题指标较高</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="18" t="inlineStr">
         <is>
-          <t>③ 主观诉求高 · 热线独证（体检未印证 · 7 个）</t>
+          <t>③ 诉求呼声高（体检未发现 · 7 个社区）</t>
         </is>
       </c>
       <c r="B17" s="19" t="n"/>
@@ -2066,8 +2058,7 @@
       </c>
       <c r="G18" s="22" t="inlineStr">
         <is>
-          <t>主观诉求高
-体检未印证</t>
+          <t>群众诉求呼声较高</t>
         </is>
       </c>
     </row>
@@ -2096,8 +2087,7 @@
       </c>
       <c r="G19" s="22" t="inlineStr">
         <is>
-          <t>主观诉求高
-体检未印证</t>
+          <t>群众诉求呼声较高</t>
         </is>
       </c>
     </row>
@@ -2126,8 +2116,7 @@
       </c>
       <c r="G20" s="22" t="inlineStr">
         <is>
-          <t>主观诉求高
-体检未印证</t>
+          <t>群众诉求呼声较高</t>
         </is>
       </c>
     </row>
@@ -2156,8 +2145,7 @@
       </c>
       <c r="G21" s="22" t="inlineStr">
         <is>
-          <t>主观诉求高
-体检未印证</t>
+          <t>群众诉求呼声较高</t>
         </is>
       </c>
     </row>
@@ -2186,8 +2174,7 @@
       </c>
       <c r="G22" s="22" t="inlineStr">
         <is>
-          <t>主观诉求高
-体检未印证</t>
+          <t>群众诉求呼声较高</t>
         </is>
       </c>
     </row>
@@ -2216,8 +2203,7 @@
       </c>
       <c r="G23" s="22" t="inlineStr">
         <is>
-          <t>主观诉求高
-体检未印证</t>
+          <t>群众诉求呼声较高</t>
         </is>
       </c>
     </row>
@@ -2246,8 +2232,7 @@
       </c>
       <c r="G24" s="22" t="inlineStr">
         <is>
-          <t>主观诉求高
-体检未印证</t>
+          <t>群众诉求呼声较高</t>
         </is>
       </c>
     </row>
@@ -2313,7 +2298,7 @@
     <row r="2">
       <c r="A2" s="8" t="inlineStr">
         <is>
-          <t>① 双高 · 体检+诉求都高（5 个）</t>
+          <t>① 双高（体检问题+群众诉求 · 5 个社区）</t>
         </is>
       </c>
       <c r="B2" s="9" t="n"/>
@@ -2342,7 +2327,7 @@
       </c>
       <c r="F3" s="12" t="inlineStr">
         <is>
-          <t>双高 ★</t>
+          <t>双高</t>
         </is>
       </c>
     </row>
@@ -2366,7 +2351,7 @@
       </c>
       <c r="F4" s="12" t="inlineStr">
         <is>
-          <t>双高 ★</t>
+          <t>双高</t>
         </is>
       </c>
     </row>
@@ -2390,7 +2375,7 @@
       </c>
       <c r="F5" s="12" t="inlineStr">
         <is>
-          <t>双高 ★</t>
+          <t>双高</t>
         </is>
       </c>
     </row>
@@ -2414,7 +2399,7 @@
       </c>
       <c r="F6" s="12" t="inlineStr">
         <is>
-          <t>双高 ★</t>
+          <t>双高</t>
         </is>
       </c>
     </row>
@@ -2438,14 +2423,14 @@
       </c>
       <c r="F7" s="12" t="inlineStr">
         <is>
-          <t>双高 ★</t>
+          <t>双高</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="13" t="inlineStr">
         <is>
-          <t>② 客观隐患高 · 体检独证（诉求未暴露 · 8 个）</t>
+          <t>② 问题指标高（诉求未反映 · 8 个社区）</t>
         </is>
       </c>
       <c r="B8" s="14" t="n"/>
@@ -2474,8 +2459,7 @@
       </c>
       <c r="F9" s="17" t="inlineStr">
         <is>
-          <t>客观隐患高
-诉求未暴露</t>
+          <t>体检问题指标较高</t>
         </is>
       </c>
     </row>
@@ -2499,8 +2483,7 @@
       </c>
       <c r="F10" s="17" t="inlineStr">
         <is>
-          <t>客观隐患高
-诉求未暴露</t>
+          <t>体检问题指标较高</t>
         </is>
       </c>
     </row>
@@ -2524,8 +2507,7 @@
       </c>
       <c r="F11" s="17" t="inlineStr">
         <is>
-          <t>客观隐患高
-诉求未暴露</t>
+          <t>体检问题指标较高</t>
         </is>
       </c>
     </row>
@@ -2549,8 +2531,7 @@
       </c>
       <c r="F12" s="17" t="inlineStr">
         <is>
-          <t>客观隐患高
-诉求未暴露</t>
+          <t>体检问题指标较高</t>
         </is>
       </c>
     </row>
@@ -2574,8 +2555,7 @@
       </c>
       <c r="F13" s="17" t="inlineStr">
         <is>
-          <t>客观隐患高
-诉求未暴露</t>
+          <t>体检问题指标较高</t>
         </is>
       </c>
     </row>
@@ -2599,8 +2579,7 @@
       </c>
       <c r="F14" s="17" t="inlineStr">
         <is>
-          <t>客观隐患高
-诉求未暴露</t>
+          <t>体检问题指标较高</t>
         </is>
       </c>
     </row>
@@ -2624,8 +2603,7 @@
       </c>
       <c r="F15" s="17" t="inlineStr">
         <is>
-          <t>客观隐患高
-诉求未暴露</t>
+          <t>体检问题指标较高</t>
         </is>
       </c>
     </row>
@@ -2649,15 +2627,14 @@
       </c>
       <c r="F16" s="17" t="inlineStr">
         <is>
-          <t>客观隐患高
-诉求未暴露</t>
+          <t>体检问题指标较高</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="18" t="inlineStr">
         <is>
-          <t>③ 主观诉求高 · 热线独证（体检未印证 · 7 个）</t>
+          <t>③ 诉求呼声高（体检未发现 · 7 个社区）</t>
         </is>
       </c>
       <c r="B17" s="19" t="n"/>
@@ -2686,8 +2663,7 @@
       </c>
       <c r="F18" s="22" t="inlineStr">
         <is>
-          <t>主观诉求高
-体检未印证</t>
+          <t>群众诉求呼声较高</t>
         </is>
       </c>
     </row>
@@ -2711,8 +2687,7 @@
       </c>
       <c r="F19" s="22" t="inlineStr">
         <is>
-          <t>主观诉求高
-体检未印证</t>
+          <t>群众诉求呼声较高</t>
         </is>
       </c>
     </row>
@@ -2736,8 +2711,7 @@
       </c>
       <c r="F20" s="22" t="inlineStr">
         <is>
-          <t>主观诉求高
-体检未印证</t>
+          <t>群众诉求呼声较高</t>
         </is>
       </c>
     </row>
@@ -2761,8 +2735,7 @@
       </c>
       <c r="F21" s="22" t="inlineStr">
         <is>
-          <t>主观诉求高
-体检未印证</t>
+          <t>群众诉求呼声较高</t>
         </is>
       </c>
     </row>
@@ -2786,8 +2759,7 @@
       </c>
       <c r="F22" s="22" t="inlineStr">
         <is>
-          <t>主观诉求高
-体检未印证</t>
+          <t>群众诉求呼声较高</t>
         </is>
       </c>
     </row>
@@ -2811,8 +2783,7 @@
       </c>
       <c r="F23" s="22" t="inlineStr">
         <is>
-          <t>主观诉求高
-体检未印证</t>
+          <t>群众诉求呼声较高</t>
         </is>
       </c>
     </row>
@@ -2836,8 +2807,7 @@
       </c>
       <c r="F24" s="22" t="inlineStr">
         <is>
-          <t>主观诉求高
-体检未印证</t>
+          <t>群众诉求呼声较高</t>
         </is>
       </c>
     </row>

--- a/DATA/analysis/page7小结/page7_分组汇总_2026-08-14_最终.xlsx
+++ b/DATA/analysis/page7小结/page7_分组汇总_2026-08-14_最终.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Github\emotion_map\DATA\analysis\page7小结\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C97E050-4A2E-4A3F-9E5C-2C53D028F9EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8959A4F4-CE5A-4942-AF34-3D59AA2B5655}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="7950" yWindow="3090" windowWidth="24135" windowHeight="17040" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1原表" sheetId="1" r:id="rId1"/>
@@ -281,6 +281,7 @@
       <sz val="11"/>
       <color rgb="FF808080"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
@@ -309,6 +310,7 @@
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
@@ -316,6 +318,7 @@
       <sz val="11"/>
       <color rgb="FFC00000"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
@@ -323,6 +326,7 @@
       <sz val="11"/>
       <color rgb="FF1F4E79"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
@@ -330,6 +334,7 @@
       <sz val="11"/>
       <color rgb="FFC55A11"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
@@ -520,11 +525,47 @@
     <xf numFmtId="0" fontId="8" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -537,42 +578,6 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -888,40 +893,40 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="39" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="28" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="14" t="s">
+      <c r="B1" s="28" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="14" t="s">
+      <c r="C1" s="28" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="14" t="s">
+      <c r="D1" s="28" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="15"/>
-      <c r="F1" s="14" t="s">
+      <c r="E1" s="30"/>
+      <c r="F1" s="28" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="15"/>
-      <c r="H1" s="14" t="s">
+      <c r="G1" s="30"/>
+      <c r="H1" s="28" t="s">
         <v>5</v>
       </c>
-      <c r="I1" s="14" t="s">
+      <c r="I1" s="28" t="s">
         <v>6</v>
       </c>
-      <c r="J1" s="14" t="s">
+      <c r="J1" s="28" t="s">
         <v>7</v>
       </c>
-      <c r="K1" s="14" t="s">
+      <c r="K1" s="28" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="2" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A2" s="16"/>
-      <c r="B2" s="16"/>
-      <c r="C2" s="16"/>
+      <c r="A2" s="29"/>
+      <c r="B2" s="29"/>
+      <c r="C2" s="29"/>
       <c r="D2" s="2" t="s">
         <v>9</v>
       </c>
@@ -934,10 +939,10 @@
       <c r="G2" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="H2" s="16"/>
-      <c r="I2" s="16"/>
-      <c r="J2" s="16"/>
-      <c r="K2" s="16"/>
+      <c r="H2" s="29"/>
+      <c r="I2" s="29"/>
+      <c r="J2" s="29"/>
+      <c r="K2" s="29"/>
     </row>
     <row r="3" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="3">
@@ -1611,15 +1616,15 @@
     </row>
   </sheetData>
   <mergeCells count="9">
+    <mergeCell ref="K1:K2"/>
+    <mergeCell ref="I1:I2"/>
+    <mergeCell ref="J1:J2"/>
+    <mergeCell ref="H1:H2"/>
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="D1:E1"/>
     <mergeCell ref="C1:C2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="F1:G1"/>
-    <mergeCell ref="K1:K2"/>
-    <mergeCell ref="I1:I2"/>
-    <mergeCell ref="J1:J2"/>
-    <mergeCell ref="H1:H2"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="D3:D22">
@@ -1699,15 +1704,15 @@
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A2" s="19" t="s">
+      <c r="A2" s="33" t="s">
         <v>42</v>
       </c>
-      <c r="B2" s="20"/>
-      <c r="C2" s="20"/>
-      <c r="D2" s="20"/>
-      <c r="E2" s="20"/>
-      <c r="F2" s="20"/>
-      <c r="G2" s="20"/>
+      <c r="B2" s="34"/>
+      <c r="C2" s="34"/>
+      <c r="D2" s="34"/>
+      <c r="E2" s="34"/>
+      <c r="F2" s="34"/>
+      <c r="G2" s="34"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A3" s="5">
@@ -1825,15 +1830,15 @@
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A8" s="17" t="s">
+      <c r="A8" s="31" t="s">
         <v>48</v>
       </c>
-      <c r="B8" s="18"/>
-      <c r="C8" s="18"/>
-      <c r="D8" s="18"/>
-      <c r="E8" s="18"/>
-      <c r="F8" s="18"/>
-      <c r="G8" s="18"/>
+      <c r="B8" s="32"/>
+      <c r="C8" s="32"/>
+      <c r="D8" s="32"/>
+      <c r="E8" s="32"/>
+      <c r="F8" s="32"/>
+      <c r="G8" s="32"/>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A9" s="8">
@@ -2020,15 +2025,15 @@
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A17" s="21" t="s">
+      <c r="A17" s="35" t="s">
         <v>59</v>
       </c>
-      <c r="B17" s="22"/>
-      <c r="C17" s="22"/>
-      <c r="D17" s="22"/>
-      <c r="E17" s="22"/>
-      <c r="F17" s="22"/>
-      <c r="G17" s="22"/>
+      <c r="B17" s="36"/>
+      <c r="C17" s="36"/>
+      <c r="D17" s="36"/>
+      <c r="E17" s="36"/>
+      <c r="F17" s="36"/>
+      <c r="G17" s="36"/>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A18" s="11">
@@ -2208,7 +2213,7 @@
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
-    <col min="2" max="2" width="14.375" style="36" customWidth="1"/>
+    <col min="2" max="2" width="14.375" style="21" customWidth="1"/>
     <col min="3" max="3" width="7" customWidth="1"/>
     <col min="4" max="4" width="18" customWidth="1"/>
     <col min="5" max="5" width="18.375" customWidth="1"/>
@@ -2216,22 +2221,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="30" x14ac:dyDescent="0.15">
-      <c r="A1" s="23" t="s">
+      <c r="A1" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="23" t="s">
+      <c r="B1" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="23" t="s">
+      <c r="C1" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="23" t="s">
+      <c r="D1" s="14" t="s">
         <v>68</v>
       </c>
-      <c r="E1" s="23" t="s">
+      <c r="E1" s="14" t="s">
         <v>69</v>
       </c>
-      <c r="F1" s="23" t="s">
+      <c r="F1" s="14" t="s">
         <v>7</v>
       </c>
     </row>
@@ -2246,422 +2251,422 @@
       <c r="F2" s="25"/>
     </row>
     <row r="3" spans="1:6" ht="16.5" x14ac:dyDescent="0.15">
-      <c r="A3" s="26">
+      <c r="A3" s="15">
         <v>1</v>
       </c>
-      <c r="B3" s="26" t="s">
+      <c r="B3" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="C3" s="26">
+      <c r="C3" s="15">
         <v>66</v>
       </c>
-      <c r="D3" s="26">
+      <c r="D3" s="15">
         <v>56.1</v>
       </c>
-      <c r="E3" s="26">
+      <c r="E3" s="15">
         <v>177.3</v>
       </c>
-      <c r="F3" s="27" t="s">
+      <c r="F3" s="16" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="16.5" x14ac:dyDescent="0.15">
-      <c r="A4" s="26">
+      <c r="A4" s="15">
         <v>2</v>
       </c>
-      <c r="B4" s="26" t="s">
+      <c r="B4" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="C4" s="26">
+      <c r="C4" s="15">
         <v>94</v>
       </c>
-      <c r="D4" s="26">
+      <c r="D4" s="15">
         <v>30.9</v>
       </c>
-      <c r="E4" s="26">
+      <c r="E4" s="15">
         <v>166</v>
       </c>
-      <c r="F4" s="27" t="s">
+      <c r="F4" s="16" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="16.5" x14ac:dyDescent="0.15">
-      <c r="A5" s="26">
+      <c r="A5" s="15">
         <v>3</v>
       </c>
-      <c r="B5" s="26" t="s">
+      <c r="B5" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="C5" s="26">
+      <c r="C5" s="15">
         <v>39</v>
       </c>
-      <c r="D5" s="26">
+      <c r="D5" s="15">
         <v>43.6</v>
       </c>
-      <c r="E5" s="26">
+      <c r="E5" s="15">
         <v>274.39999999999998</v>
       </c>
-      <c r="F5" s="27" t="s">
+      <c r="F5" s="16" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="16.5" x14ac:dyDescent="0.15">
-      <c r="A6" s="26">
+      <c r="A6" s="15">
         <v>4</v>
       </c>
-      <c r="B6" s="26" t="s">
+      <c r="B6" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="C6" s="26">
+      <c r="C6" s="15">
         <v>44</v>
       </c>
-      <c r="D6" s="26">
+      <c r="D6" s="15">
         <v>36.4</v>
       </c>
-      <c r="E6" s="26">
+      <c r="E6" s="15">
         <v>261.39999999999998</v>
       </c>
-      <c r="F6" s="27" t="s">
+      <c r="F6" s="16" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="16.5" x14ac:dyDescent="0.15">
-      <c r="A7" s="26">
+      <c r="A7" s="15">
         <v>5</v>
       </c>
-      <c r="B7" s="26" t="s">
+      <c r="B7" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="C7" s="26">
+      <c r="C7" s="15">
         <v>30</v>
       </c>
-      <c r="D7" s="26">
+      <c r="D7" s="15">
         <v>30</v>
       </c>
-      <c r="E7" s="26">
+      <c r="E7" s="15">
         <v>370</v>
       </c>
-      <c r="F7" s="27" t="s">
+      <c r="F7" s="16" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="15" x14ac:dyDescent="0.25">
-      <c r="A8" s="28" t="s">
+      <c r="A8" s="22" t="s">
         <v>48</v>
       </c>
-      <c r="B8" s="29"/>
-      <c r="C8" s="29"/>
-      <c r="D8" s="29"/>
-      <c r="E8" s="29"/>
-      <c r="F8" s="29"/>
+      <c r="B8" s="23"/>
+      <c r="C8" s="23"/>
+      <c r="D8" s="23"/>
+      <c r="E8" s="23"/>
+      <c r="F8" s="23"/>
     </row>
     <row r="9" spans="1:6" ht="16.5" x14ac:dyDescent="0.15">
-      <c r="A9" s="30">
+      <c r="A9" s="17">
         <v>6</v>
       </c>
-      <c r="B9" s="30" t="s">
+      <c r="B9" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="C9" s="30">
+      <c r="C9" s="17">
         <v>127</v>
       </c>
-      <c r="D9" s="30">
+      <c r="D9" s="17">
         <v>84.3</v>
       </c>
-      <c r="E9" s="30">
+      <c r="E9" s="17">
         <v>5.5</v>
       </c>
-      <c r="F9" s="31" t="s">
+      <c r="F9" s="18" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="16.5" x14ac:dyDescent="0.15">
-      <c r="A10" s="30">
+      <c r="A10" s="17">
         <v>7</v>
       </c>
-      <c r="B10" s="30" t="s">
+      <c r="B10" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="C10" s="30">
+      <c r="C10" s="17">
         <v>78</v>
       </c>
-      <c r="D10" s="30">
+      <c r="D10" s="17">
         <v>116.7</v>
       </c>
-      <c r="E10" s="30">
+      <c r="E10" s="17">
         <v>44.9</v>
       </c>
-      <c r="F10" s="31" t="s">
+      <c r="F10" s="18" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="16.5" x14ac:dyDescent="0.15">
-      <c r="A11" s="30">
+      <c r="A11" s="17">
         <v>8</v>
       </c>
-      <c r="B11" s="30" t="s">
+      <c r="B11" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="C11" s="30">
+      <c r="C11" s="17">
         <v>56</v>
       </c>
-      <c r="D11" s="30">
+      <c r="D11" s="17">
         <v>150</v>
       </c>
-      <c r="E11" s="30">
+      <c r="E11" s="17">
         <v>35.700000000000003</v>
       </c>
-      <c r="F11" s="31" t="s">
+      <c r="F11" s="18" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="16.5" x14ac:dyDescent="0.15">
-      <c r="A12" s="30">
+      <c r="A12" s="17">
         <v>9</v>
       </c>
-      <c r="B12" s="30" t="s">
+      <c r="B12" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="C12" s="30">
+      <c r="C12" s="17">
         <v>78</v>
       </c>
-      <c r="D12" s="30">
+      <c r="D12" s="17">
         <v>105.1</v>
       </c>
-      <c r="E12" s="30">
+      <c r="E12" s="17">
         <v>6.4</v>
       </c>
-      <c r="F12" s="31" t="s">
+      <c r="F12" s="18" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="16.5" x14ac:dyDescent="0.15">
-      <c r="A13" s="30">
+      <c r="A13" s="17">
         <v>10</v>
       </c>
-      <c r="B13" s="30" t="s">
+      <c r="B13" s="17" t="s">
         <v>22</v>
       </c>
-      <c r="C13" s="30">
+      <c r="C13" s="17">
         <v>58</v>
       </c>
-      <c r="D13" s="30">
+      <c r="D13" s="17">
         <v>112.1</v>
       </c>
-      <c r="E13" s="30">
+      <c r="E13" s="17">
         <v>1.7</v>
       </c>
-      <c r="F13" s="31" t="s">
+      <c r="F13" s="18" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="16.5" x14ac:dyDescent="0.15">
-      <c r="A14" s="30">
+      <c r="A14" s="17">
         <v>11</v>
       </c>
-      <c r="B14" s="30" t="s">
+      <c r="B14" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="C14" s="30">
+      <c r="C14" s="17">
         <v>130</v>
       </c>
-      <c r="D14" s="30">
+      <c r="D14" s="17">
         <v>47.7</v>
       </c>
-      <c r="E14" s="30">
+      <c r="E14" s="17">
         <v>49.2</v>
       </c>
-      <c r="F14" s="31" t="s">
+      <c r="F14" s="18" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="16.5" x14ac:dyDescent="0.15">
-      <c r="A15" s="30">
+      <c r="A15" s="17">
         <v>12</v>
       </c>
-      <c r="B15" s="30" t="s">
+      <c r="B15" s="17" t="s">
         <v>24</v>
       </c>
-      <c r="C15" s="30">
+      <c r="C15" s="17">
         <v>93</v>
       </c>
-      <c r="D15" s="30">
+      <c r="D15" s="17">
         <v>54.8</v>
       </c>
-      <c r="E15" s="30">
+      <c r="E15" s="17">
         <v>78.5</v>
       </c>
-      <c r="F15" s="31" t="s">
+      <c r="F15" s="18" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="16.5" x14ac:dyDescent="0.15">
-      <c r="A16" s="30">
+      <c r="A16" s="17">
         <v>13</v>
       </c>
-      <c r="B16" s="30" t="s">
+      <c r="B16" s="17" t="s">
         <v>25</v>
       </c>
-      <c r="C16" s="30">
+      <c r="C16" s="17">
         <v>48</v>
       </c>
-      <c r="D16" s="30">
+      <c r="D16" s="17">
         <v>77.099999999999994</v>
       </c>
-      <c r="E16" s="30">
+      <c r="E16" s="17">
         <v>0</v>
       </c>
-      <c r="F16" s="31" t="s">
+      <c r="F16" s="18" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="15" x14ac:dyDescent="0.25">
-      <c r="A17" s="32" t="s">
+      <c r="A17" s="26" t="s">
         <v>59</v>
       </c>
-      <c r="B17" s="33"/>
-      <c r="C17" s="33"/>
-      <c r="D17" s="33"/>
-      <c r="E17" s="33"/>
-      <c r="F17" s="33"/>
+      <c r="B17" s="27"/>
+      <c r="C17" s="27"/>
+      <c r="D17" s="27"/>
+      <c r="E17" s="27"/>
+      <c r="F17" s="27"/>
     </row>
     <row r="18" spans="1:6" ht="16.5" x14ac:dyDescent="0.15">
-      <c r="A18" s="34">
+      <c r="A18" s="19">
         <v>14</v>
       </c>
-      <c r="B18" s="34" t="s">
+      <c r="B18" s="19" t="s">
         <v>26</v>
       </c>
-      <c r="C18" s="34">
+      <c r="C18" s="19">
         <v>84</v>
       </c>
-      <c r="D18" s="34">
+      <c r="D18" s="19">
         <v>13.1</v>
       </c>
-      <c r="E18" s="34">
+      <c r="E18" s="19">
         <v>707.1</v>
       </c>
-      <c r="F18" s="35" t="s">
+      <c r="F18" s="20" t="s">
         <v>61</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="16.5" x14ac:dyDescent="0.15">
-      <c r="A19" s="34">
+      <c r="A19" s="19">
         <v>15</v>
       </c>
-      <c r="B19" s="34" t="s">
+      <c r="B19" s="19" t="s">
         <v>28</v>
       </c>
-      <c r="C19" s="34">
+      <c r="C19" s="19">
         <v>69</v>
       </c>
-      <c r="D19" s="34">
+      <c r="D19" s="19">
         <v>10.1</v>
       </c>
-      <c r="E19" s="34">
+      <c r="E19" s="19">
         <v>726.1</v>
       </c>
-      <c r="F19" s="35" t="s">
+      <c r="F19" s="20" t="s">
         <v>61</v>
       </c>
     </row>
     <row r="20" spans="1:6" ht="16.5" x14ac:dyDescent="0.15">
-      <c r="A20" s="34">
+      <c r="A20" s="19">
         <v>16</v>
       </c>
-      <c r="B20" s="34" t="s">
+      <c r="B20" s="19" t="s">
         <v>29</v>
       </c>
-      <c r="C20" s="34">
+      <c r="C20" s="19">
         <v>106</v>
       </c>
-      <c r="D20" s="34">
+      <c r="D20" s="19">
         <v>16</v>
       </c>
-      <c r="E20" s="34">
+      <c r="E20" s="19">
         <v>393.4</v>
       </c>
-      <c r="F20" s="35" t="s">
+      <c r="F20" s="20" t="s">
         <v>61</v>
       </c>
     </row>
     <row r="21" spans="1:6" ht="16.5" x14ac:dyDescent="0.15">
-      <c r="A21" s="34">
+      <c r="A21" s="19">
         <v>17</v>
       </c>
-      <c r="B21" s="34" t="s">
+      <c r="B21" s="19" t="s">
         <v>30</v>
       </c>
-      <c r="C21" s="34">
+      <c r="C21" s="19">
         <v>66</v>
       </c>
-      <c r="D21" s="34">
+      <c r="D21" s="19">
         <v>13.6</v>
       </c>
-      <c r="E21" s="34">
+      <c r="E21" s="19">
         <v>563.6</v>
       </c>
-      <c r="F21" s="35" t="s">
+      <c r="F21" s="20" t="s">
         <v>61</v>
       </c>
     </row>
     <row r="22" spans="1:6" ht="16.5" x14ac:dyDescent="0.15">
-      <c r="A22" s="34">
+      <c r="A22" s="19">
         <v>18</v>
       </c>
-      <c r="B22" s="34" t="s">
+      <c r="B22" s="19" t="s">
         <v>31</v>
       </c>
-      <c r="C22" s="34">
+      <c r="C22" s="19">
         <v>83</v>
       </c>
-      <c r="D22" s="34">
+      <c r="D22" s="19">
         <v>2.4</v>
       </c>
-      <c r="E22" s="34">
+      <c r="E22" s="19">
         <v>271.10000000000002</v>
       </c>
-      <c r="F22" s="35" t="s">
+      <c r="F22" s="20" t="s">
         <v>61</v>
       </c>
     </row>
     <row r="23" spans="1:6" ht="16.5" x14ac:dyDescent="0.15">
-      <c r="A23" s="34">
+      <c r="A23" s="19">
         <v>19</v>
       </c>
-      <c r="B23" s="34" t="s">
+      <c r="B23" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="C23" s="34">
+      <c r="C23" s="19">
         <v>97</v>
       </c>
-      <c r="D23" s="34">
+      <c r="D23" s="19">
         <v>7.2</v>
       </c>
-      <c r="E23" s="34">
+      <c r="E23" s="19">
         <v>228.9</v>
       </c>
-      <c r="F23" s="35" t="s">
+      <c r="F23" s="20" t="s">
         <v>61</v>
       </c>
     </row>
     <row r="24" spans="1:6" ht="16.5" x14ac:dyDescent="0.15">
-      <c r="A24" s="34">
+      <c r="A24" s="19">
         <v>20</v>
       </c>
-      <c r="B24" s="34" t="s">
+      <c r="B24" s="19" t="s">
         <v>33</v>
       </c>
-      <c r="C24" s="34">
+      <c r="C24" s="19">
         <v>55</v>
       </c>
-      <c r="D24" s="34">
+      <c r="D24" s="19">
         <v>14.5</v>
       </c>
-      <c r="E24" s="34">
+      <c r="E24" s="19">
         <v>401.8</v>
       </c>
-      <c r="F24" s="35" t="s">
+      <c r="F24" s="20" t="s">
         <v>61</v>
       </c>
     </row>
